--- a/01_raw_data/4.1_SOCS/raw/input/D2.6.SVY.LABR.xlsx
+++ b/01_raw_data/4.1_SOCS/raw/input/D2.6.SVY.LABR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28906"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/bstacy_worldbank_org/Documents/DECIS/SPI/Data/SPI 2023/01_raw_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/spi/technical-work/SPI-Zander/SPI/01_raw_data/4.1_SOCS/raw/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{CCE5EEBB-4D58-4017-8091-E111410662AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE1EE2DD-3C5D-4662-A2CF-EFA921C66581}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{CCE5EEBB-4D58-4017-8091-E111410662AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D519CE79-D075-6B4A-8647-9EC626E78545}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{B1D4A2B0-B996-4285-8899-E61063B05042}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" firstSheet="1" activeTab="1" xr2:uid="{B1D4A2B0-B996-4285-8899-E61063B05042}"/>
   </bookViews>
   <sheets>
     <sheet name="2020 DCS" sheetId="13" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2020 DCS'!$A$2:$AB$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$C$3:$AH$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$C$3:$AI$3</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -4678,7 +4678,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General_)"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5044,9 +5044,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5084,7 +5084,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5190,7 +5190,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5332,7 +5332,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5341,12 +5341,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C22CDDB-AEF5-4276-8A85-C94955DAB41B}">
   <dimension ref="A1:AB192"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -5437,7 +5437,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -6211,7 +6211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -6383,7 +6383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -6469,7 +6469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -6641,7 +6641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>50</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -7329,7 +7329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -7415,7 +7415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:28">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -7501,7 +7501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:28">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:28">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:28">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:28">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:28">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -7931,7 +7931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:28">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>59</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:28">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:28">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -8189,7 +8189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:28">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:28">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>63</v>
       </c>
@@ -8361,7 +8361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:28">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>64</v>
       </c>
@@ -8447,7 +8447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:28">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:28">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:28">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>67</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:28">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>68</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:28">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>69</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:28">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:28">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>71</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:28">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>72</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:28">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>73</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:28">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -9307,7 +9307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:28">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:28">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>76</v>
       </c>
@@ -9479,7 +9479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:28">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:28">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:28">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>79</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:28">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -9823,7 +9823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:28">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>81</v>
       </c>
@@ -9909,7 +9909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:28">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:28">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -10081,7 +10081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:28">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:28">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>85</v>
       </c>
@@ -10253,7 +10253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:28">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>86</v>
       </c>
@@ -10339,7 +10339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:28">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>87</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:28">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>88</v>
       </c>
@@ -10511,7 +10511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:28">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>89</v>
       </c>
@@ -10597,7 +10597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:28">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>90</v>
       </c>
@@ -10683,7 +10683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:28">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -10769,7 +10769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:28">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>92</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:28">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>93</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:28">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>94</v>
       </c>
@@ -11027,7 +11027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:28">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>95</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:28">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>96</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:28">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>97</v>
       </c>
@@ -11285,7 +11285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:28">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>98</v>
       </c>
@@ -11371,7 +11371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:28">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>99</v>
       </c>
@@ -11457,7 +11457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:28">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -11543,7 +11543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:28">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>101</v>
       </c>
@@ -11629,7 +11629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:28">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>102</v>
       </c>
@@ -11715,7 +11715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:28">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>103</v>
       </c>
@@ -11801,7 +11801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:28">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>104</v>
       </c>
@@ -11887,7 +11887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:28">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>105</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:28">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>106</v>
       </c>
@@ -12059,7 +12059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:28">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>107</v>
       </c>
@@ -12145,7 +12145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:28">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>108</v>
       </c>
@@ -12231,7 +12231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:28">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>109</v>
       </c>
@@ -12317,7 +12317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:28">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>110</v>
       </c>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:28">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>111</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:28">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>112</v>
       </c>
@@ -12575,7 +12575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:28">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>113</v>
       </c>
@@ -12661,7 +12661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:28">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>114</v>
       </c>
@@ -12747,7 +12747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:28">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>115</v>
       </c>
@@ -12833,7 +12833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:28">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>116</v>
       </c>
@@ -12919,7 +12919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:28">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>117</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:28">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>118</v>
       </c>
@@ -13091,7 +13091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:28">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>119</v>
       </c>
@@ -13177,7 +13177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:28">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>120</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:28">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>121</v>
       </c>
@@ -13349,7 +13349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:28">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>122</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:28">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>123</v>
       </c>
@@ -13521,7 +13521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:28">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>124</v>
       </c>
@@ -13607,7 +13607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:28">
+    <row r="98" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>125</v>
       </c>
@@ -13693,7 +13693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:28">
+    <row r="99" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>126</v>
       </c>
@@ -13779,7 +13779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:28">
+    <row r="100" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>127</v>
       </c>
@@ -13865,7 +13865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:28">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>128</v>
       </c>
@@ -13951,7 +13951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:28">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>129</v>
       </c>
@@ -14037,7 +14037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:28">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>130</v>
       </c>
@@ -14123,7 +14123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:28">
+    <row r="104" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>131</v>
       </c>
@@ -14209,7 +14209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:28">
+    <row r="105" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>132</v>
       </c>
@@ -14295,7 +14295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:28">
+    <row r="106" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>133</v>
       </c>
@@ -14381,7 +14381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:28">
+    <row r="107" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>134</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:28">
+    <row r="108" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>135</v>
       </c>
@@ -14553,7 +14553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:28">
+    <row r="109" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>136</v>
       </c>
@@ -14639,7 +14639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:28">
+    <row r="110" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>137</v>
       </c>
@@ -14725,7 +14725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:28">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>138</v>
       </c>
@@ -14811,7 +14811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:28">
+    <row r="112" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>139</v>
       </c>
@@ -14897,7 +14897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>140</v>
       </c>
@@ -14983,7 +14983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>141</v>
       </c>
@@ -15069,7 +15069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:28">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>142</v>
       </c>
@@ -15155,7 +15155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>143</v>
       </c>
@@ -15241,7 +15241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>144</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>145</v>
       </c>
@@ -15413,7 +15413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>146</v>
       </c>
@@ -15499,7 +15499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>147</v>
       </c>
@@ -15585,7 +15585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>148</v>
       </c>
@@ -15671,7 +15671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>149</v>
       </c>
@@ -15757,7 +15757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>150</v>
       </c>
@@ -15843,7 +15843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:28">
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>151</v>
       </c>
@@ -15929,7 +15929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>152</v>
       </c>
@@ -16015,7 +16015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>153</v>
       </c>
@@ -16101,7 +16101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>154</v>
       </c>
@@ -16187,7 +16187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>155</v>
       </c>
@@ -16273,7 +16273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>156</v>
       </c>
@@ -16359,7 +16359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>157</v>
       </c>
@@ -16445,7 +16445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>158</v>
       </c>
@@ -16531,7 +16531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>159</v>
       </c>
@@ -16617,7 +16617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>160</v>
       </c>
@@ -16703,7 +16703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>161</v>
       </c>
@@ -16789,7 +16789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>162</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>163</v>
       </c>
@@ -16961,7 +16961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>164</v>
       </c>
@@ -17047,7 +17047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>165</v>
       </c>
@@ -17133,7 +17133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>166</v>
       </c>
@@ -17219,7 +17219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>167</v>
       </c>
@@ -17305,7 +17305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:28">
+    <row r="141" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>168</v>
       </c>
@@ -17391,7 +17391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:28">
+    <row r="142" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>169</v>
       </c>
@@ -17477,7 +17477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:28">
+    <row r="143" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>170</v>
       </c>
@@ -17563,7 +17563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:28">
+    <row r="144" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>171</v>
       </c>
@@ -17649,7 +17649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:28">
+    <row r="145" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>172</v>
       </c>
@@ -17735,7 +17735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:28">
+    <row r="146" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>173</v>
       </c>
@@ -17821,7 +17821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:28">
+    <row r="147" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>174</v>
       </c>
@@ -17907,7 +17907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:28">
+    <row r="148" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>175</v>
       </c>
@@ -17993,7 +17993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:28">
+    <row r="149" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>176</v>
       </c>
@@ -18079,7 +18079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:28">
+    <row r="150" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>177</v>
       </c>
@@ -18165,7 +18165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:28">
+    <row r="151" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>178</v>
       </c>
@@ -18251,7 +18251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:28">
+    <row r="152" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>179</v>
       </c>
@@ -18337,7 +18337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:28">
+    <row r="153" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>180</v>
       </c>
@@ -18423,7 +18423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:28">
+    <row r="154" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>181</v>
       </c>
@@ -18509,7 +18509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:28">
+    <row r="155" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>182</v>
       </c>
@@ -18595,7 +18595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:28">
+    <row r="156" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>183</v>
       </c>
@@ -18681,7 +18681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:28">
+    <row r="157" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>184</v>
       </c>
@@ -18767,7 +18767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:28">
+    <row r="158" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>185</v>
       </c>
@@ -18853,7 +18853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:28">
+    <row r="159" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>186</v>
       </c>
@@ -18939,7 +18939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:28">
+    <row r="160" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>187</v>
       </c>
@@ -19025,7 +19025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:28">
+    <row r="161" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -19111,7 +19111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:28">
+    <row r="162" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>189</v>
       </c>
@@ -19197,7 +19197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:28">
+    <row r="163" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>190</v>
       </c>
@@ -19283,7 +19283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:28">
+    <row r="164" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>191</v>
       </c>
@@ -19369,7 +19369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:28">
+    <row r="165" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>192</v>
       </c>
@@ -19455,7 +19455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:28">
+    <row r="166" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>193</v>
       </c>
@@ -19541,7 +19541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:28">
+    <row r="167" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>194</v>
       </c>
@@ -19627,7 +19627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:28">
+    <row r="168" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>195</v>
       </c>
@@ -19713,7 +19713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:28">
+    <row r="169" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>196</v>
       </c>
@@ -19799,7 +19799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:28">
+    <row r="170" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>197</v>
       </c>
@@ -19885,7 +19885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:28">
+    <row r="171" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>198</v>
       </c>
@@ -19971,7 +19971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:28">
+    <row r="172" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>199</v>
       </c>
@@ -20057,7 +20057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:28">
+    <row r="173" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>200</v>
       </c>
@@ -20143,7 +20143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:28">
+    <row r="174" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>201</v>
       </c>
@@ -20229,7 +20229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:28">
+    <row r="175" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>202</v>
       </c>
@@ -20315,7 +20315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:28">
+    <row r="176" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>203</v>
       </c>
@@ -20401,7 +20401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:28">
+    <row r="177" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>204</v>
       </c>
@@ -20487,7 +20487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:28">
+    <row r="178" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>205</v>
       </c>
@@ -20573,7 +20573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:28">
+    <row r="179" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>206</v>
       </c>
@@ -20659,7 +20659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:28">
+    <row r="180" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>207</v>
       </c>
@@ -20745,7 +20745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:28">
+    <row r="181" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>208</v>
       </c>
@@ -20831,7 +20831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:28">
+    <row r="182" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>209</v>
       </c>
@@ -20917,7 +20917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:28">
+    <row r="183" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>210</v>
       </c>
@@ -21003,7 +21003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:28">
+    <row r="184" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>211</v>
       </c>
@@ -21089,7 +21089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:28">
+    <row r="185" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>212</v>
       </c>
@@ -21175,7 +21175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:28">
+    <row r="186" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>213</v>
       </c>
@@ -21261,7 +21261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:28">
+    <row r="187" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>214</v>
       </c>
@@ -21347,7 +21347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:28">
+    <row r="188" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>215</v>
       </c>
@@ -21433,7 +21433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:28">
+    <row r="189" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>216</v>
       </c>
@@ -21519,7 +21519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:28">
+    <row r="190" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>217</v>
       </c>
@@ -21605,7 +21605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:28">
+    <row r="191" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>218</v>
       </c>
@@ -21691,7 +21691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:28">
+    <row r="192" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>219</v>
       </c>
@@ -21780,28 +21780,30 @@
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CF2AA0-498C-4EC1-BF25-39656B9B0E42}">
-  <dimension ref="A1:CB193"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:CC193"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="4.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="2" customWidth="1"/>
-    <col min="5" max="6" width="9.5703125" style="2" customWidth="1"/>
-    <col min="7" max="28" width="8.85546875"/>
-    <col min="29" max="29" width="8.7109375"/>
-    <col min="34" max="34" width="156.28515625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="22" style="29" customWidth="1"/>
-    <col min="36" max="36" width="22.28515625" style="29" customWidth="1"/>
-    <col min="37" max="37" width="23" style="29" customWidth="1"/>
-    <col min="38" max="79" width="8.85546875" style="29"/>
+    <col min="1" max="2" width="4.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" style="2" customWidth="1"/>
+    <col min="5" max="6" width="9.5" style="2" hidden="1" customWidth="1"/>
+    <col min="7" max="29" width="0" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="156.33203125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="22" style="29" customWidth="1"/>
+    <col min="37" max="37" width="22.33203125" style="29" customWidth="1"/>
+    <col min="38" max="38" width="23" style="29" customWidth="1"/>
+    <col min="39" max="80" width="8.83203125" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D1" s="20" t="s">
         <v>220</v>
       </c>
@@ -21813,7 +21815,7 @@
       </c>
       <c r="G1" s="51"/>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C2" s="1">
         <v>1</v>
       </c>
@@ -21898,8 +21900,9 @@
       <c r="AE2" s="1"/>
       <c r="AF2" s="1"/>
       <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>223</v>
       </c>
@@ -21999,11 +22002,14 @@
       <c r="AG3" s="52">
         <v>2024</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AH3" s="52">
+        <v>2025</v>
+      </c>
+      <c r="AI3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -22099,12 +22105,13 @@
         <v>0</v>
       </c>
       <c r="AG4" s="29"/>
-      <c r="AH4" t="str">
-        <f>+IF($E4=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F4=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G4=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H4=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I4=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J4=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K4=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L4=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M4=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N4=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O4=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P4=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q4=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R4=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S4=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T4=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U4=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V4=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W4=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X4=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y4=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z4=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA4=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB4=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC4=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD4=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE4=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF4=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG4=1, RIGHT(AG$3,4)&amp;", ", "")</f>
+      <c r="AH4" s="29"/>
+      <c r="AI4" t="str">
+        <f>+IF($E4=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F4=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G4=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H4=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I4=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J4=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K4=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L4=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M4=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N4=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O4=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P4=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q4=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R4=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S4=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T4=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U4=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V4=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W4=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X4=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y4=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z4=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA4=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB4=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC4=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD4=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE4=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF4=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG4=1, RIGHT(AG$3,4)&amp;", ", "")&amp;IF($AH4=1, RIGHT(AH$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2013, </v>
       </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -22196,12 +22203,13 @@
       <c r="AE5" s="29"/>
       <c r="AF5" s="29"/>
       <c r="AG5" s="29"/>
-      <c r="AH5" t="str">
-        <f t="shared" ref="AH5:AH68" si="0">+IF($E5=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F5=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G5=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H5=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I5=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J5=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K5=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L5=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M5=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N5=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O5=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P5=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q5=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R5=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S5=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T5=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U5=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V5=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W5=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X5=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y5=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z5=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA5=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB5=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC5=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD5=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE5=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF5=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG5=1, RIGHT(AG$3,4)&amp;", ", "")</f>
+      <c r="AH5" s="29"/>
+      <c r="AI5" t="str">
+        <f t="shared" ref="AI5:AI68" si="0">+IF($E5=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F5=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G5=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H5=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I5=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J5=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K5=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L5=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M5=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N5=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O5=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P5=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q5=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R5=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S5=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T5=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U5=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V5=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W5=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X5=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y5=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z5=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA5=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB5=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC5=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD5=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE5=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF5=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG5=1, RIGHT(AG$3,4)&amp;", ", "")&amp;IF($AH5=1, RIGHT(AH$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2009, 2010, 2011, 2019, </v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -22293,12 +22301,13 @@
       <c r="AE6" s="29"/>
       <c r="AF6" s="29"/>
       <c r="AG6" s="29"/>
-      <c r="AH6" t="str">
-        <f t="shared" si="0"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" t="str">
+        <f>+IF($E6=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F6=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G6=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H6=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I6=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J6=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K6=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L6=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M6=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N6=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O6=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P6=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q6=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R6=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S6=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T6=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U6=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V6=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W6=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X6=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y6=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z6=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA6=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB6=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC6=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD6=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE6=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF6=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG6=1, RIGHT(AG$3,4)&amp;", ", "")&amp;IF($AH6=1, RIGHT(AH$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, </v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -22390,12 +22399,13 @@
       <c r="AE7" s="29"/>
       <c r="AF7" s="29"/>
       <c r="AG7" s="29"/>
-      <c r="AH7" t="str">
+      <c r="AH7" s="29"/>
+      <c r="AI7" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -22487,12 +22497,13 @@
       <c r="AE8" s="29"/>
       <c r="AF8" s="29"/>
       <c r="AG8" s="29"/>
-      <c r="AH8" t="str">
+      <c r="AH8" s="29"/>
+      <c r="AI8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2006, 2007, 2008, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -22584,12 +22595,13 @@
       <c r="AE9" s="29"/>
       <c r="AF9" s="29"/>
       <c r="AG9" s="29"/>
-      <c r="AH9" t="str">
+      <c r="AH9" s="29"/>
+      <c r="AI9" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>7</v>
       </c>
@@ -22681,12 +22693,13 @@
       <c r="AE10" s="29"/>
       <c r="AF10" s="29"/>
       <c r="AG10" s="29"/>
-      <c r="AH10" t="str">
+      <c r="AH10" s="29"/>
+      <c r="AI10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2010, 2011, </v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -22778,12 +22791,13 @@
       <c r="AE11" s="29"/>
       <c r="AF11" s="29"/>
       <c r="AG11" s="29"/>
-      <c r="AH11" t="str">
+      <c r="AH11" s="29"/>
+      <c r="AI11" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2005, </v>
       </c>
     </row>
-    <row r="12" spans="1:34">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -22875,12 +22889,13 @@
       <c r="AE12" s="29"/>
       <c r="AF12" s="29"/>
       <c r="AG12" s="29"/>
-      <c r="AH12" t="str">
+      <c r="AH12" s="29"/>
+      <c r="AI12" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2001, 2011, 2018, </v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>10</v>
       </c>
@@ -22974,12 +22989,13 @@
         <v>1</v>
       </c>
       <c r="AG13" s="29"/>
-      <c r="AH13" t="str">
+      <c r="AH13" s="29"/>
+      <c r="AI13" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2006, 2018, 2023, </v>
       </c>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -23071,12 +23087,13 @@
       <c r="AE14" s="29"/>
       <c r="AF14" s="29"/>
       <c r="AG14" s="29"/>
-      <c r="AH14" t="str">
+      <c r="AH14" s="29"/>
+      <c r="AI14" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2001, 2002, 2004, 2006, 2009, 2010, 2013, 2015, 2016, 2017, </v>
       </c>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>12</v>
       </c>
@@ -23168,12 +23185,13 @@
       <c r="AE15" s="29"/>
       <c r="AF15" s="29"/>
       <c r="AG15" s="29"/>
-      <c r="AH15" t="str">
+      <c r="AH15" s="29"/>
+      <c r="AI15" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>13</v>
       </c>
@@ -23265,12 +23283,13 @@
       <c r="AE16" s="29"/>
       <c r="AF16" s="29"/>
       <c r="AG16" s="29"/>
-      <c r="AH16" t="str">
+      <c r="AH16" s="29"/>
+      <c r="AI16" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="17" spans="1:79">
+    <row r="17" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -23362,12 +23381,13 @@
       <c r="AE17" s="29"/>
       <c r="AF17" s="29"/>
       <c r="AG17" s="29"/>
-      <c r="AH17" t="str">
+      <c r="AH17" s="29"/>
+      <c r="AI17" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2016, 2017, </v>
       </c>
     </row>
-    <row r="18" spans="1:79">
+    <row r="18" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -23459,12 +23479,13 @@
       <c r="AE18" s="29"/>
       <c r="AF18" s="29"/>
       <c r="AG18" s="29"/>
-      <c r="AH18" t="str">
+      <c r="AH18" s="29"/>
+      <c r="AI18" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2007, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="19" spans="1:79">
+    <row r="19" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>16</v>
       </c>
@@ -23556,12 +23577,13 @@
       <c r="AE19" s="29"/>
       <c r="AF19" s="29"/>
       <c r="AG19" s="29"/>
-      <c r="AH19" t="str">
+      <c r="AH19" s="29"/>
+      <c r="AI19" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="20" spans="1:79">
+    <row r="20" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>17</v>
       </c>
@@ -23653,12 +23675,13 @@
       <c r="AE20" s="29"/>
       <c r="AF20" s="29"/>
       <c r="AG20" s="29"/>
-      <c r="AH20" t="str">
+      <c r="AH20" s="29"/>
+      <c r="AI20" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, </v>
       </c>
     </row>
-    <row r="21" spans="1:79" s="15" customFormat="1">
+    <row r="21" spans="1:80" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>18</v>
       </c>
@@ -23752,11 +23775,11 @@
       </c>
       <c r="AF21" s="29"/>
       <c r="AG21" s="29"/>
-      <c r="AH21" t="str">
+      <c r="AH21" s="29"/>
+      <c r="AI21" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2009, 2010, 2011, 2012, 2018, 2019, 2022, </v>
       </c>
-      <c r="AI21" s="29"/>
       <c r="AJ21" s="29"/>
       <c r="AK21" s="29"/>
       <c r="AL21" s="29"/>
@@ -23801,8 +23824,9 @@
       <c r="BY21" s="29"/>
       <c r="BZ21" s="29"/>
       <c r="CA21" s="29"/>
+      <c r="CB21" s="29"/>
     </row>
-    <row r="22" spans="1:79">
+    <row r="22" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>19</v>
       </c>
@@ -23894,12 +23918,13 @@
       <c r="AE22" s="29"/>
       <c r="AF22" s="29"/>
       <c r="AG22" s="29"/>
-      <c r="AH22" t="str">
+      <c r="AH22" s="29"/>
+      <c r="AI22" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1996, 2006, </v>
       </c>
     </row>
-    <row r="23" spans="1:79">
+    <row r="23" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>20</v>
       </c>
@@ -23991,12 +24016,13 @@
       <c r="AE23" s="29"/>
       <c r="AF23" s="29"/>
       <c r="AG23" s="29"/>
-      <c r="AH23" t="str">
+      <c r="AH23" s="29"/>
+      <c r="AI23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:79">
+    <row r="24" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>21</v>
       </c>
@@ -24088,12 +24114,13 @@
       <c r="AE24" s="29"/>
       <c r="AF24" s="29"/>
       <c r="AG24" s="29"/>
-      <c r="AH24" t="str">
+      <c r="AH24" s="29"/>
+      <c r="AI24" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="25" spans="1:79">
+    <row r="25" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>22</v>
       </c>
@@ -24185,12 +24212,13 @@
       <c r="AE25" s="29"/>
       <c r="AF25" s="29"/>
       <c r="AG25" s="29"/>
-      <c r="AH25" t="str">
+      <c r="AH25" s="29"/>
+      <c r="AI25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2010, 2011, </v>
       </c>
     </row>
-    <row r="26" spans="1:79">
+    <row r="26" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>23</v>
       </c>
@@ -24282,12 +24310,13 @@
       <c r="AE26" s="29"/>
       <c r="AF26" s="29"/>
       <c r="AG26" s="29"/>
-      <c r="AH26" t="str">
+      <c r="AH26" s="29"/>
+      <c r="AI26" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2012, 2013, 2017, </v>
       </c>
     </row>
-    <row r="27" spans="1:79">
+    <row r="27" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>24</v>
       </c>
@@ -24379,12 +24408,13 @@
       <c r="AE27" s="29"/>
       <c r="AF27" s="29"/>
       <c r="AG27" s="29"/>
-      <c r="AH27" t="str">
+      <c r="AH27" s="29"/>
+      <c r="AI27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2010, </v>
       </c>
     </row>
-    <row r="28" spans="1:79">
+    <row r="28" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>25</v>
       </c>
@@ -24478,12 +24508,13 @@
       <c r="AE28" s="29"/>
       <c r="AF28" s="29"/>
       <c r="AG28" s="29"/>
-      <c r="AH28" t="str">
+      <c r="AH28" s="29"/>
+      <c r="AI28" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2005, 2012, 2021, </v>
       </c>
     </row>
-    <row r="29" spans="1:79" s="15" customFormat="1">
+    <row r="29" spans="1:80" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -24575,11 +24606,11 @@
       <c r="AE29" s="29"/>
       <c r="AF29" s="29"/>
       <c r="AG29" s="29"/>
-      <c r="AH29" t="str">
+      <c r="AH29" s="29"/>
+      <c r="AI29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AI29" s="29"/>
       <c r="AJ29" s="29"/>
       <c r="AK29" s="29"/>
       <c r="AL29" s="29"/>
@@ -24624,8 +24655,9 @@
       <c r="BY29" s="29"/>
       <c r="BZ29" s="29"/>
       <c r="CA29" s="29"/>
+      <c r="CB29" s="29"/>
     </row>
-    <row r="30" spans="1:79">
+    <row r="30" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>27</v>
       </c>
@@ -24717,12 +24749,13 @@
       <c r="AE30" s="29"/>
       <c r="AF30" s="29"/>
       <c r="AG30" s="29"/>
-      <c r="AH30" t="str">
+      <c r="AH30" s="29"/>
+      <c r="AI30" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="31" spans="1:79">
+    <row r="31" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>28</v>
       </c>
@@ -24814,12 +24847,13 @@
       <c r="AE31" s="29"/>
       <c r="AF31" s="29"/>
       <c r="AG31" s="29"/>
-      <c r="AH31" t="str">
+      <c r="AH31" s="29"/>
+      <c r="AI31" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2014, </v>
       </c>
     </row>
-    <row r="32" spans="1:79">
+    <row r="32" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>29</v>
       </c>
@@ -24911,12 +24945,13 @@
       <c r="AE32" s="29"/>
       <c r="AF32" s="29"/>
       <c r="AG32" s="29"/>
-      <c r="AH32" t="str">
+      <c r="AH32" s="29"/>
+      <c r="AI32" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2009, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="33" spans="1:79">
+    <row r="33" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>30</v>
       </c>
@@ -25008,12 +25043,13 @@
       <c r="AE33" s="53"/>
       <c r="AF33" s="53"/>
       <c r="AG33" s="53"/>
-      <c r="AH33" t="str">
+      <c r="AH33" s="53"/>
+      <c r="AI33" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, </v>
       </c>
     </row>
-    <row r="34" spans="1:79">
+    <row r="34" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>31</v>
       </c>
@@ -25105,12 +25141,13 @@
       <c r="AE34" s="29"/>
       <c r="AF34" s="29"/>
       <c r="AG34" s="29"/>
-      <c r="AH34" t="str">
+      <c r="AH34" s="29"/>
+      <c r="AI34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:79">
+    <row r="35" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>32</v>
       </c>
@@ -25202,12 +25239,13 @@
       <c r="AE35" s="29"/>
       <c r="AF35" s="29"/>
       <c r="AG35" s="29"/>
-      <c r="AH35" t="str">
+      <c r="AH35" s="29"/>
+      <c r="AI35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:79">
+    <row r="36" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>33</v>
       </c>
@@ -25299,12 +25337,13 @@
       <c r="AE36" s="29"/>
       <c r="AF36" s="29"/>
       <c r="AG36" s="29"/>
-      <c r="AH36" t="str">
+      <c r="AH36" s="29"/>
+      <c r="AI36" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="37" spans="1:79" s="15" customFormat="1">
+    <row r="37" spans="1:80" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>34</v>
       </c>
@@ -25396,11 +25435,11 @@
       <c r="AE37" s="29"/>
       <c r="AF37" s="29"/>
       <c r="AG37" s="29"/>
-      <c r="AH37" t="str">
+      <c r="AH37" s="29"/>
+      <c r="AI37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AI37" s="29"/>
       <c r="AJ37" s="29"/>
       <c r="AK37" s="29"/>
       <c r="AL37" s="29"/>
@@ -25445,8 +25484,9 @@
       <c r="BY37" s="29"/>
       <c r="BZ37" s="29"/>
       <c r="CA37" s="29"/>
+      <c r="CB37" s="29"/>
     </row>
-    <row r="38" spans="1:79">
+    <row r="38" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>35</v>
       </c>
@@ -25538,12 +25578,13 @@
       <c r="AE38" s="29"/>
       <c r="AF38" s="29"/>
       <c r="AG38" s="29"/>
-      <c r="AH38" t="str">
+      <c r="AH38" s="29"/>
+      <c r="AI38" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="39" spans="1:79">
+    <row r="39" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>36</v>
       </c>
@@ -25637,12 +25678,13 @@
       </c>
       <c r="AF39" s="29"/>
       <c r="AG39" s="29"/>
-      <c r="AH39" t="str">
+      <c r="AH39" s="29"/>
+      <c r="AI39" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1998, 2004, 2006, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2022, </v>
       </c>
     </row>
-    <row r="40" spans="1:79">
+    <row r="40" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>37</v>
       </c>
@@ -25734,12 +25776,13 @@
       <c r="AE40" s="29"/>
       <c r="AF40" s="29"/>
       <c r="AG40" s="29"/>
-      <c r="AH40" t="str">
+      <c r="AH40" s="29"/>
+      <c r="AI40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:79">
+    <row r="41" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>38</v>
       </c>
@@ -25831,12 +25874,13 @@
       <c r="AE41" s="29"/>
       <c r="AF41" s="29"/>
       <c r="AG41" s="29"/>
-      <c r="AH41" t="str">
+      <c r="AH41" s="29"/>
+      <c r="AI41" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1999, 2005, 2008, 2013, </v>
       </c>
     </row>
-    <row r="42" spans="1:79">
+    <row r="42" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <v>39</v>
       </c>
@@ -25928,12 +25972,13 @@
       <c r="AE42" s="29"/>
       <c r="AF42" s="29"/>
       <c r="AG42" s="29"/>
-      <c r="AH42" t="str">
+      <c r="AH42" s="29"/>
+      <c r="AI42" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2004, 2005, 2010, 2011, 2015, 2016, </v>
       </c>
     </row>
-    <row r="43" spans="1:79">
+    <row r="43" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <v>40</v>
       </c>
@@ -26025,12 +26070,13 @@
       <c r="AE43" s="29"/>
       <c r="AF43" s="29"/>
       <c r="AG43" s="29"/>
-      <c r="AH43" t="str">
+      <c r="AH43" s="29"/>
+      <c r="AI43" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:79">
+    <row r="44" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <v>41</v>
       </c>
@@ -26122,12 +26168,13 @@
       <c r="AE44" s="29"/>
       <c r="AF44" s="29"/>
       <c r="AG44" s="29"/>
-      <c r="AH44" t="str">
+      <c r="AH44" s="29"/>
+      <c r="AI44" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2012, </v>
       </c>
     </row>
-    <row r="45" spans="1:79">
+    <row r="45" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
         <v>42</v>
       </c>
@@ -26223,12 +26270,13 @@
         <v>1</v>
       </c>
       <c r="AG45" s="29"/>
-      <c r="AH45" t="str">
+      <c r="AH45" s="29"/>
+      <c r="AI45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2022, 2023, </v>
       </c>
     </row>
-    <row r="46" spans="1:79">
+    <row r="46" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
         <v>43</v>
       </c>
@@ -26320,12 +26368,13 @@
       <c r="AE46" s="29"/>
       <c r="AF46" s="29"/>
       <c r="AG46" s="29"/>
-      <c r="AH46" t="str">
+      <c r="AH46" s="29"/>
+      <c r="AI46" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2012, 2015, </v>
       </c>
     </row>
-    <row r="47" spans="1:79">
+    <row r="47" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
         <v>44</v>
       </c>
@@ -26417,12 +26466,13 @@
       <c r="AE47" s="29"/>
       <c r="AF47" s="29"/>
       <c r="AG47" s="29"/>
-      <c r="AH47" t="str">
+      <c r="AH47" s="29"/>
+      <c r="AI47" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:79">
+    <row r="48" spans="1:80" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
         <v>45</v>
       </c>
@@ -26514,12 +26564,13 @@
       <c r="AE48" s="29"/>
       <c r="AF48" s="29"/>
       <c r="AG48" s="29"/>
-      <c r="AH48" t="str">
+      <c r="AH48" s="29"/>
+      <c r="AI48" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2012, 2018, </v>
       </c>
     </row>
-    <row r="49" spans="1:34">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <v>46</v>
       </c>
@@ -26611,12 +26662,13 @@
       <c r="AE49" s="29"/>
       <c r="AF49" s="29"/>
       <c r="AG49" s="29"/>
-      <c r="AH49" t="str">
+      <c r="AH49" s="29"/>
+      <c r="AI49" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:34">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
         <v>47</v>
       </c>
@@ -26708,12 +26760,13 @@
       <c r="AE50" s="29"/>
       <c r="AF50" s="29"/>
       <c r="AG50" s="29"/>
-      <c r="AH50" t="str">
+      <c r="AH50" s="29"/>
+      <c r="AI50" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:34">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
         <v>48</v>
       </c>
@@ -26805,12 +26858,13 @@
       <c r="AE51" s="29"/>
       <c r="AF51" s="29"/>
       <c r="AG51" s="29"/>
-      <c r="AH51" t="str">
+      <c r="AH51" s="29"/>
+      <c r="AI51" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:34">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <v>49</v>
       </c>
@@ -26902,12 +26956,13 @@
       <c r="AE52" s="29"/>
       <c r="AF52" s="29"/>
       <c r="AG52" s="29"/>
-      <c r="AH52" t="str">
+      <c r="AH52" s="29"/>
+      <c r="AI52" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2003, 2004, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="53" spans="1:34">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <v>50</v>
       </c>
@@ -26999,12 +27054,13 @@
       <c r="AE53" s="29"/>
       <c r="AF53" s="29"/>
       <c r="AG53" s="29"/>
-      <c r="AH53" t="str">
+      <c r="AH53" s="29"/>
+      <c r="AI53" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="54" spans="1:34">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>51</v>
       </c>
@@ -27100,12 +27156,13 @@
       </c>
       <c r="AF54" s="29"/>
       <c r="AG54" s="29"/>
-      <c r="AH54" t="str">
+      <c r="AH54" s="29"/>
+      <c r="AI54" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2001, 2002, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
     </row>
-    <row r="55" spans="1:34">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>52</v>
       </c>
@@ -27197,12 +27254,13 @@
       <c r="AE55" s="29"/>
       <c r="AF55" s="29"/>
       <c r="AG55" s="29"/>
-      <c r="AH55" t="str">
+      <c r="AH55" s="29"/>
+      <c r="AI55" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="56" spans="1:34">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>53</v>
       </c>
@@ -27294,12 +27352,13 @@
       <c r="AE56" s="29"/>
       <c r="AF56" s="29"/>
       <c r="AG56" s="29"/>
-      <c r="AH56" t="str">
+      <c r="AH56" s="29"/>
+      <c r="AI56" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:34">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>54</v>
       </c>
@@ -27391,12 +27450,13 @@
       <c r="AE57" s="29"/>
       <c r="AF57" s="29"/>
       <c r="AG57" s="29"/>
-      <c r="AH57" t="str">
+      <c r="AH57" s="29"/>
+      <c r="AI57" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="58" spans="1:34">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>55</v>
       </c>
@@ -27488,12 +27548,13 @@
       <c r="AE58" s="29"/>
       <c r="AF58" s="29"/>
       <c r="AG58" s="29"/>
-      <c r="AH58" t="str">
+      <c r="AH58" s="29"/>
+      <c r="AI58" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2000, 2004, 2005, 2006, 2007, 2009, 2011, 2018, </v>
       </c>
     </row>
-    <row r="59" spans="1:34">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>56</v>
       </c>
@@ -27585,12 +27646,13 @@
       <c r="AE59" s="29"/>
       <c r="AF59" s="29"/>
       <c r="AG59" s="29"/>
-      <c r="AH59" t="str">
+      <c r="AH59" s="29"/>
+      <c r="AI59" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="60" spans="1:34">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>57</v>
       </c>
@@ -27682,12 +27744,13 @@
       <c r="AE60" s="29"/>
       <c r="AF60" s="29"/>
       <c r="AG60" s="29"/>
-      <c r="AH60" t="str">
+      <c r="AH60" s="29"/>
+      <c r="AI60" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:34">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>58</v>
       </c>
@@ -27779,12 +27842,13 @@
       <c r="AE61" s="53"/>
       <c r="AF61" s="53"/>
       <c r="AG61" s="53"/>
-      <c r="AH61" t="str">
+      <c r="AH61" s="53"/>
+      <c r="AI61" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2004, 2005, 2006, 2007, 2008, 2009, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, </v>
       </c>
     </row>
-    <row r="62" spans="1:34">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>59</v>
       </c>
@@ -27876,12 +27940,13 @@
       <c r="AE62" s="29"/>
       <c r="AF62" s="29"/>
       <c r="AG62" s="29"/>
-      <c r="AH62" t="str">
+      <c r="AH62" s="29"/>
+      <c r="AI62" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, </v>
       </c>
     </row>
-    <row r="63" spans="1:34">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>60</v>
       </c>
@@ -27973,12 +28038,13 @@
       <c r="AE63" s="29"/>
       <c r="AF63" s="29"/>
       <c r="AG63" s="29"/>
-      <c r="AH63" t="str">
+      <c r="AH63" s="29"/>
+      <c r="AI63" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2008, 2009, 2010, 2011, 2012, 2013, </v>
       </c>
     </row>
-    <row r="64" spans="1:34">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <v>61</v>
       </c>
@@ -28070,12 +28136,13 @@
       <c r="AE64" s="29"/>
       <c r="AF64" s="29"/>
       <c r="AG64" s="29"/>
-      <c r="AH64" t="str">
+      <c r="AH64" s="29"/>
+      <c r="AI64" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">1999, </v>
       </c>
     </row>
-    <row r="65" spans="1:34">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A65" s="5">
         <v>62</v>
       </c>
@@ -28167,12 +28234,13 @@
       <c r="AE65" s="29"/>
       <c r="AF65" s="29"/>
       <c r="AG65" s="29"/>
-      <c r="AH65" t="str">
+      <c r="AH65" s="29"/>
+      <c r="AI65" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2018, </v>
       </c>
     </row>
-    <row r="66" spans="1:34">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A66" s="5">
         <v>63</v>
       </c>
@@ -28264,12 +28332,13 @@
       <c r="AE66" s="29"/>
       <c r="AF66" s="29"/>
       <c r="AG66" s="29"/>
-      <c r="AH66" t="str">
+      <c r="AH66" s="29"/>
+      <c r="AI66" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">2000, 2001, 2012, </v>
       </c>
     </row>
-    <row r="67" spans="1:34">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A67" s="5">
         <v>64</v>
       </c>
@@ -28361,12 +28430,13 @@
       <c r="AE67" s="29"/>
       <c r="AF67" s="29"/>
       <c r="AG67" s="29"/>
-      <c r="AH67" t="str">
+      <c r="AH67" s="29"/>
+      <c r="AI67" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:34">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <v>65</v>
       </c>
@@ -28458,12 +28528,13 @@
       <c r="AE68" s="29"/>
       <c r="AF68" s="29"/>
       <c r="AG68" s="29"/>
-      <c r="AH68" t="str">
+      <c r="AH68" s="29"/>
+      <c r="AI68" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:34">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <v>66</v>
       </c>
@@ -28555,12 +28626,13 @@
       <c r="AE69" s="29"/>
       <c r="AF69" s="29"/>
       <c r="AG69" s="29"/>
-      <c r="AH69" t="str">
-        <f t="shared" ref="AH69:AH132" si="1">+IF($E69=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F69=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G69=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H69=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I69=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J69=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K69=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L69=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M69=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N69=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O69=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P69=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q69=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R69=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S69=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T69=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U69=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V69=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W69=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X69=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y69=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z69=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA69=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB69=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC69=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD69=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE69=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF69=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG69=1, RIGHT(AG$3,4)&amp;", ", "")</f>
+      <c r="AH69" s="29"/>
+      <c r="AI69" t="str">
+        <f t="shared" ref="AI69:AI132" si="1">+IF($E69=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F69=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G69=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H69=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I69=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J69=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K69=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L69=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M69=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N69=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O69=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P69=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q69=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R69=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S69=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T69=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U69=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V69=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W69=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X69=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y69=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z69=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA69=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB69=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC69=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD69=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE69=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF69=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG69=1, RIGHT(AG$3,4)&amp;", ", "")&amp;IF($AH69=1, RIGHT(AH$3,4)&amp;", ", "")</f>
         <v xml:space="preserve">2009, 2010, 2017, </v>
       </c>
     </row>
-    <row r="70" spans="1:34">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <v>67</v>
       </c>
@@ -28652,12 +28724,13 @@
       <c r="AE70" s="29"/>
       <c r="AF70" s="29"/>
       <c r="AG70" s="29"/>
-      <c r="AH70" t="str">
+      <c r="AH70" s="29"/>
+      <c r="AI70" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2019, </v>
       </c>
     </row>
-    <row r="71" spans="1:34">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <v>68</v>
       </c>
@@ -28749,12 +28822,13 @@
       <c r="AE71" s="29"/>
       <c r="AF71" s="29"/>
       <c r="AG71" s="29"/>
-      <c r="AH71" t="str">
+      <c r="AH71" s="29"/>
+      <c r="AI71" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2010, </v>
       </c>
     </row>
-    <row r="72" spans="1:34">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A72" s="5">
         <v>69</v>
       </c>
@@ -28846,12 +28920,13 @@
       <c r="AE72" s="29"/>
       <c r="AF72" s="29"/>
       <c r="AG72" s="29"/>
-      <c r="AH72" t="str">
+      <c r="AH72" s="29"/>
+      <c r="AI72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:34">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A73" s="5">
         <v>70</v>
       </c>
@@ -28943,12 +29018,13 @@
       <c r="AE73" s="29"/>
       <c r="AF73" s="29"/>
       <c r="AG73" s="29"/>
-      <c r="AH73" t="str">
+      <c r="AH73" s="29"/>
+      <c r="AI73" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2011, 2012, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="74" spans="1:34">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A74" s="5">
         <v>71</v>
       </c>
@@ -29040,12 +29116,13 @@
       <c r="AE74" s="29"/>
       <c r="AF74" s="29"/>
       <c r="AG74" s="29"/>
-      <c r="AH74" t="str">
+      <c r="AH74" s="29"/>
+      <c r="AI74" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="75" spans="1:34">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A75" s="5">
         <v>72</v>
       </c>
@@ -29137,12 +29214,13 @@
       <c r="AE75" s="29"/>
       <c r="AF75" s="29"/>
       <c r="AG75" s="29"/>
-      <c r="AH75" t="str">
+      <c r="AH75" s="29"/>
+      <c r="AI75" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2008, </v>
       </c>
     </row>
-    <row r="76" spans="1:34">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A76" s="5">
         <v>73</v>
       </c>
@@ -29234,12 +29312,13 @@
       <c r="AE76" s="29"/>
       <c r="AF76" s="29"/>
       <c r="AG76" s="29"/>
-      <c r="AH76" t="str">
+      <c r="AH76" s="29"/>
+      <c r="AI76" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">1999, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="77" spans="1:34">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <f t="shared" ref="A77:A125" si="2">1+A76</f>
         <v>74</v>
@@ -29336,12 +29415,13 @@
       </c>
       <c r="AF77" s="29"/>
       <c r="AG77" s="29"/>
-      <c r="AH77" t="str">
+      <c r="AH77" s="29"/>
+      <c r="AI77" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
     </row>
-    <row r="78" spans="1:34">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -29434,12 +29514,13 @@
       <c r="AE78" s="29"/>
       <c r="AF78" s="29"/>
       <c r="AG78" s="29"/>
-      <c r="AH78" t="str">
+      <c r="AH78" s="29"/>
+      <c r="AI78" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2012, 2015, </v>
       </c>
     </row>
-    <row r="79" spans="1:34">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -29532,12 +29613,13 @@
       <c r="AE79" s="29"/>
       <c r="AF79" s="29"/>
       <c r="AG79" s="29"/>
-      <c r="AH79" t="str">
+      <c r="AH79" s="29"/>
+      <c r="AI79" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:34">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -29630,12 +29712,13 @@
       <c r="AE80" s="29"/>
       <c r="AF80" s="29"/>
       <c r="AG80" s="29"/>
-      <c r="AH80" t="str">
+      <c r="AH80" s="29"/>
+      <c r="AI80" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="81" spans="1:34">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A81" s="5">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -29728,12 +29811,13 @@
       <c r="AE81" s="29"/>
       <c r="AF81" s="29"/>
       <c r="AG81" s="29"/>
-      <c r="AH81" t="str">
+      <c r="AH81" s="29"/>
+      <c r="AI81" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:34">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -29826,12 +29910,13 @@
       <c r="AE82" s="29"/>
       <c r="AF82" s="29"/>
       <c r="AG82" s="29"/>
-      <c r="AH82" t="str">
+      <c r="AH82" s="29"/>
+      <c r="AI82" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="83" spans="1:34">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -29924,12 +30009,13 @@
       <c r="AE83" s="29"/>
       <c r="AF83" s="29"/>
       <c r="AG83" s="29"/>
-      <c r="AH83" t="str">
+      <c r="AH83" s="29"/>
+      <c r="AI83" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2013, 2016, 2017, 2018, </v>
       </c>
     </row>
-    <row r="84" spans="1:34">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -30022,12 +30108,13 @@
       <c r="AE84" s="29"/>
       <c r="AF84" s="29"/>
       <c r="AG84" s="29"/>
-      <c r="AH84" t="str">
+      <c r="AH84" s="29"/>
+      <c r="AI84" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2015, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="85" spans="1:34">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -30120,12 +30207,13 @@
       <c r="AE85" s="53"/>
       <c r="AF85" s="53"/>
       <c r="AG85" s="53"/>
-      <c r="AH85" t="str">
+      <c r="AH85" s="53"/>
+      <c r="AI85" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, </v>
       </c>
     </row>
-    <row r="86" spans="1:34">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -30218,12 +30306,13 @@
       <c r="AE86" s="29"/>
       <c r="AF86" s="29"/>
       <c r="AG86" s="29"/>
-      <c r="AH86" t="str">
+      <c r="AH86" s="29"/>
+      <c r="AI86" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2002, 2006, 2007, 2008, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="87" spans="1:34">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -30316,12 +30405,13 @@
       <c r="AE87" s="29"/>
       <c r="AF87" s="29"/>
       <c r="AG87" s="29"/>
-      <c r="AH87" t="str">
+      <c r="AH87" s="29"/>
+      <c r="AI87" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2004, </v>
       </c>
     </row>
-    <row r="88" spans="1:34">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -30414,12 +30504,13 @@
       <c r="AE88" s="29"/>
       <c r="AF88" s="29"/>
       <c r="AG88" s="29"/>
-      <c r="AH88" t="str">
+      <c r="AH88" s="29"/>
+      <c r="AI88" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2012, 2017, </v>
       </c>
     </row>
-    <row r="89" spans="1:34">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -30512,12 +30603,13 @@
       <c r="AE89" s="53"/>
       <c r="AF89" s="53"/>
       <c r="AG89" s="53"/>
-      <c r="AH89" t="str">
+      <c r="AH89" s="53"/>
+      <c r="AI89" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="90" spans="1:34">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -30610,12 +30702,13 @@
       <c r="AE90" s="29"/>
       <c r="AF90" s="29"/>
       <c r="AG90" s="29"/>
-      <c r="AH90" t="str">
+      <c r="AH90" s="29"/>
+      <c r="AI90" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2012, 2013, </v>
       </c>
     </row>
-    <row r="91" spans="1:34">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -30708,12 +30801,13 @@
       <c r="AE91" s="54"/>
       <c r="AF91" s="54"/>
       <c r="AG91" s="54"/>
-      <c r="AH91" t="str">
+      <c r="AH91" s="54"/>
+      <c r="AI91" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, </v>
       </c>
     </row>
-    <row r="92" spans="1:34">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -30806,12 +30900,13 @@
       <c r="AE92" s="29"/>
       <c r="AF92" s="29"/>
       <c r="AG92" s="29"/>
-      <c r="AH92" t="str">
+      <c r="AH92" s="29"/>
+      <c r="AI92" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2012, 2013, 2014, 2016, 2018, </v>
       </c>
     </row>
-    <row r="93" spans="1:34">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -30904,12 +30999,13 @@
       <c r="AE93" s="29"/>
       <c r="AF93" s="29"/>
       <c r="AG93" s="29"/>
-      <c r="AH93" t="str">
+      <c r="AH93" s="29"/>
+      <c r="AI93" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2012, 2017, </v>
       </c>
     </row>
-    <row r="94" spans="1:34">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -31002,12 +31098,13 @@
       <c r="AE94" s="29"/>
       <c r="AF94" s="29"/>
       <c r="AG94" s="29"/>
-      <c r="AH94" t="str">
+      <c r="AH94" s="29"/>
+      <c r="AI94" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2012, </v>
       </c>
     </row>
-    <row r="95" spans="1:34">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -31100,12 +31197,13 @@
       <c r="AE95" s="29"/>
       <c r="AF95" s="29"/>
       <c r="AG95" s="29"/>
-      <c r="AH95" t="str">
+      <c r="AH95" s="29"/>
+      <c r="AI95" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2009, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="96" spans="1:34">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -31198,12 +31296,13 @@
       <c r="AE96" s="29"/>
       <c r="AF96" s="29"/>
       <c r="AG96" s="29"/>
-      <c r="AH96" t="str">
+      <c r="AH96" s="29"/>
+      <c r="AI96" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">1998, 2008, 2017, </v>
       </c>
     </row>
-    <row r="97" spans="1:34">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -31296,12 +31395,13 @@
       <c r="AE97" s="29"/>
       <c r="AF97" s="29"/>
       <c r="AG97" s="29"/>
-      <c r="AH97" t="str">
+      <c r="AH97" s="29"/>
+      <c r="AI97" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:34">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -31394,12 +31494,13 @@
       <c r="AE98" s="29"/>
       <c r="AF98" s="29"/>
       <c r="AG98" s="29"/>
-      <c r="AH98" t="str">
+      <c r="AH98" s="29"/>
+      <c r="AI98" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">1999, 2001, 2003, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2017, </v>
       </c>
     </row>
-    <row r="99" spans="1:34">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -31492,12 +31593,13 @@
       <c r="AE99" s="53"/>
       <c r="AF99" s="53"/>
       <c r="AG99" s="53"/>
-      <c r="AH99" t="str">
+      <c r="AH99" s="53"/>
+      <c r="AI99" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="100" spans="1:34">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -31590,12 +31692,13 @@
       <c r="AE100" s="53"/>
       <c r="AF100" s="53"/>
       <c r="AG100" s="53"/>
-      <c r="AH100" t="str">
+      <c r="AH100" s="53"/>
+      <c r="AI100" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="101" spans="1:34">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -31688,12 +31791,13 @@
       <c r="AE101" s="29"/>
       <c r="AF101" s="29"/>
       <c r="AG101" s="29"/>
-      <c r="AH101" t="str">
+      <c r="AH101" s="29"/>
+      <c r="AI101" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="102" spans="1:34">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -31786,12 +31890,13 @@
       <c r="AE102" s="29"/>
       <c r="AF102" s="29"/>
       <c r="AG102" s="29"/>
-      <c r="AH102" t="str">
+      <c r="AH102" s="29"/>
+      <c r="AI102" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:34">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -31884,12 +31989,13 @@
       <c r="AE103" s="29"/>
       <c r="AF103" s="29"/>
       <c r="AG103" s="29"/>
-      <c r="AH103" t="str">
+      <c r="AH103" s="29"/>
+      <c r="AI103" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:34">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -31986,12 +32092,13 @@
       </c>
       <c r="AF104" s="29"/>
       <c r="AG104" s="29"/>
-      <c r="AH104" t="str">
+      <c r="AH104" s="29"/>
+      <c r="AI104" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
     </row>
-    <row r="105" spans="1:34">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -32084,12 +32191,13 @@
       <c r="AE105" s="29"/>
       <c r="AF105" s="29"/>
       <c r="AG105" s="29"/>
-      <c r="AH105" t="str">
+      <c r="AH105" s="29"/>
+      <c r="AI105" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, </v>
       </c>
     </row>
-    <row r="106" spans="1:34">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -32182,12 +32290,13 @@
       <c r="AE106" s="29"/>
       <c r="AF106" s="29"/>
       <c r="AG106" s="29"/>
-      <c r="AH106" t="str">
+      <c r="AH106" s="29"/>
+      <c r="AI106" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="107" spans="1:34">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -32284,12 +32393,13 @@
       </c>
       <c r="AF107" s="29"/>
       <c r="AG107" s="29"/>
-      <c r="AH107" t="str">
+      <c r="AH107" s="29"/>
+      <c r="AI107" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
     </row>
-    <row r="108" spans="1:34">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -32382,12 +32492,13 @@
       <c r="AE108" s="53"/>
       <c r="AF108" s="53"/>
       <c r="AG108" s="53"/>
-      <c r="AH108" t="str">
+      <c r="AH108" s="53"/>
+      <c r="AI108" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, </v>
       </c>
     </row>
-    <row r="109" spans="1:34">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -32480,12 +32591,13 @@
       <c r="AE109" s="53"/>
       <c r="AF109" s="53"/>
       <c r="AG109" s="53"/>
-      <c r="AH109" t="str">
+      <c r="AH109" s="53"/>
+      <c r="AI109" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2011, 2016, 2017, 2018, 2019, 2020, </v>
       </c>
     </row>
-    <row r="110" spans="1:34">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -32578,12 +32690,13 @@
       <c r="AE110" s="29"/>
       <c r="AF110" s="29"/>
       <c r="AG110" s="29"/>
-      <c r="AH110" t="str">
+      <c r="AH110" s="29"/>
+      <c r="AI110" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2011, </v>
       </c>
     </row>
-    <row r="111" spans="1:34">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -32676,12 +32789,13 @@
       <c r="AE111" s="29"/>
       <c r="AF111" s="29"/>
       <c r="AG111" s="29"/>
-      <c r="AH111" t="str">
+      <c r="AH111" s="29"/>
+      <c r="AI111" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2015, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="112" spans="1:34">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -32774,12 +32888,13 @@
       <c r="AE112" s="29"/>
       <c r="AF112" s="29"/>
       <c r="AG112" s="29"/>
-      <c r="AH112" t="str">
+      <c r="AH112" s="29"/>
+      <c r="AI112" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:34">
+    <row r="113" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -32872,12 +32987,13 @@
       <c r="AE113" s="29"/>
       <c r="AF113" s="29"/>
       <c r="AG113" s="29"/>
-      <c r="AH113" t="str">
+      <c r="AH113" s="29"/>
+      <c r="AI113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2014, </v>
       </c>
     </row>
-    <row r="114" spans="1:34">
+    <row r="114" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -32970,12 +33086,13 @@
       <c r="AE114" s="29"/>
       <c r="AF114" s="29"/>
       <c r="AG114" s="29"/>
-      <c r="AH114" t="str">
+      <c r="AH114" s="29"/>
+      <c r="AI114" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:34">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -33068,12 +33185,13 @@
       <c r="AE115" s="29"/>
       <c r="AF115" s="29"/>
       <c r="AG115" s="29"/>
-      <c r="AH115" t="str">
+      <c r="AH115" s="29"/>
+      <c r="AI115" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:34">
+    <row r="116" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -33166,12 +33284,13 @@
       <c r="AE116" s="29"/>
       <c r="AF116" s="29"/>
       <c r="AG116" s="29"/>
-      <c r="AH116" t="str">
+      <c r="AH116" s="29"/>
+      <c r="AI116" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="117" spans="1:34">
+    <row r="117" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -33264,12 +33383,13 @@
       <c r="AE117" s="29"/>
       <c r="AF117" s="29"/>
       <c r="AG117" s="29"/>
-      <c r="AH117" t="str">
+      <c r="AH117" s="29"/>
+      <c r="AI117" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:34" ht="24.75">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -33362,12 +33482,13 @@
       <c r="AE118" s="29"/>
       <c r="AF118" s="29"/>
       <c r="AG118" s="29"/>
-      <c r="AH118" t="str">
+      <c r="AH118" s="29"/>
+      <c r="AI118" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:34">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -33460,12 +33581,13 @@
       <c r="AE119" s="29"/>
       <c r="AF119" s="29"/>
       <c r="AG119" s="29"/>
-      <c r="AH119" t="str">
+      <c r="AH119" s="29"/>
+      <c r="AI119" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:34">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -33558,12 +33680,13 @@
       <c r="AE120" s="29"/>
       <c r="AF120" s="29"/>
       <c r="AG120" s="29"/>
-      <c r="AH120" t="str">
+      <c r="AH120" s="29"/>
+      <c r="AI120" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2016, </v>
       </c>
     </row>
-    <row r="121" spans="1:34">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -33656,12 +33779,13 @@
       <c r="AE121" s="29"/>
       <c r="AF121" s="29"/>
       <c r="AG121" s="29"/>
-      <c r="AH121" t="str">
+      <c r="AH121" s="29"/>
+      <c r="AI121" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="122" spans="1:34">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -33754,12 +33878,13 @@
       <c r="AE122" s="29"/>
       <c r="AF122" s="29"/>
       <c r="AG122" s="29"/>
-      <c r="AH122" t="str">
+      <c r="AH122" s="29"/>
+      <c r="AI122" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2006, 2007, 2008, 2009, 2010, 2011, 2012, </v>
       </c>
     </row>
-    <row r="123" spans="1:34">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -33852,12 +33977,13 @@
       <c r="AE123" s="29"/>
       <c r="AF123" s="29"/>
       <c r="AG123" s="29"/>
-      <c r="AH123" t="str">
+      <c r="AH123" s="29"/>
+      <c r="AI123" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:34">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -33950,12 +34076,13 @@
       <c r="AE124" s="29"/>
       <c r="AF124" s="29"/>
       <c r="AG124" s="29"/>
-      <c r="AH124" t="str">
+      <c r="AH124" s="29"/>
+      <c r="AI124" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2017, </v>
       </c>
     </row>
-    <row r="125" spans="1:34">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="e">
         <f t="shared" si="2"/>
         <v>#REF!</v>
@@ -34048,12 +34175,13 @@
       <c r="AE125" s="53"/>
       <c r="AF125" s="53"/>
       <c r="AG125" s="53"/>
-      <c r="AH125" t="str">
+      <c r="AH125" s="53"/>
+      <c r="AI125" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2003, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="126" spans="1:34">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -34146,12 +34274,13 @@
       <c r="AE126" s="29"/>
       <c r="AF126" s="29"/>
       <c r="AG126" s="29"/>
-      <c r="AH126" t="str">
+      <c r="AH126" s="29"/>
+      <c r="AI126" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2004, 2009, </v>
       </c>
     </row>
-    <row r="127" spans="1:34">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="e">
         <f t="shared" ref="A127:A148" si="3">1+A126</f>
         <v>#REF!</v>
@@ -34244,12 +34373,13 @@
       <c r="AE127" s="29"/>
       <c r="AF127" s="29"/>
       <c r="AG127" s="29"/>
-      <c r="AH127" t="str">
+      <c r="AH127" s="29"/>
+      <c r="AI127" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:34">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -34342,12 +34472,13 @@
       <c r="AE128" s="29"/>
       <c r="AF128" s="29"/>
       <c r="AG128" s="29"/>
-      <c r="AH128" t="str">
+      <c r="AH128" s="29"/>
+      <c r="AI128" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2010, 2013, 2016, </v>
       </c>
     </row>
-    <row r="129" spans="1:34">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -34440,12 +34571,13 @@
       <c r="AE129" s="29"/>
       <c r="AF129" s="29"/>
       <c r="AG129" s="29"/>
-      <c r="AH129" t="str">
+      <c r="AH129" s="29"/>
+      <c r="AI129" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2003, 2018, </v>
       </c>
     </row>
-    <row r="130" spans="1:34">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -34538,12 +34670,13 @@
       <c r="AE130" s="29"/>
       <c r="AF130" s="29"/>
       <c r="AG130" s="29"/>
-      <c r="AH130" t="str">
+      <c r="AH130" s="29"/>
+      <c r="AI130" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2010, 2011, 2012, 2013, 2014, 2015, 2016, </v>
       </c>
     </row>
-    <row r="131" spans="1:34">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -34636,12 +34769,13 @@
       <c r="AE131" s="29"/>
       <c r="AF131" s="29"/>
       <c r="AG131" s="29"/>
-      <c r="AH131" t="str">
+      <c r="AH131" s="29"/>
+      <c r="AI131" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2000, 2001, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, </v>
       </c>
     </row>
-    <row r="132" spans="1:34">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -34738,12 +34872,13 @@
       </c>
       <c r="AF132" s="29"/>
       <c r="AG132" s="29"/>
-      <c r="AH132" t="str">
+      <c r="AH132" s="29"/>
+      <c r="AI132" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
     </row>
-    <row r="133" spans="1:34">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -34836,12 +34971,13 @@
       <c r="AE133" s="29"/>
       <c r="AF133" s="29"/>
       <c r="AG133" s="29"/>
-      <c r="AH133" t="str">
-        <f t="shared" ref="AH133:AH193" si="4">+IF($E133=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F133=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G133=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H133=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I133=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J133=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K133=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L133=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M133=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N133=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O133=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P133=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q133=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R133=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S133=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T133=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U133=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V133=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W133=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X133=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y133=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z133=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA133=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB133=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC133=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD133=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE133=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF133=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG133=1, RIGHT(AG$3,4)&amp;", ", "")</f>
+      <c r="AH133" s="29"/>
+      <c r="AI133" t="str">
+        <f t="shared" ref="AI133:AI193" si="4">+IF($E133=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F133=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G133=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H133=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I133=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J133=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K133=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L133=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M133=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N133=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O133=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P133=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q133=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R133=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S133=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T133=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U133=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V133=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W133=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X133=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y133=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z133=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA133=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB133=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC133=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD133=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE133=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF133=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG133=1, RIGHT(AG$3,4)&amp;", ", "")&amp;IF($AH133=1, RIGHT(AH$3,4)&amp;", ", "")</f>
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:34">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -34934,12 +35070,13 @@
       <c r="AE134" s="29"/>
       <c r="AF134" s="29"/>
       <c r="AG134" s="29"/>
-      <c r="AH134" t="str">
+      <c r="AH134" s="29"/>
+      <c r="AI134" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2000, 2001, 2006, 2014, </v>
       </c>
     </row>
-    <row r="135" spans="1:34">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -35032,12 +35169,13 @@
       <c r="AE135" s="29"/>
       <c r="AF135" s="29"/>
       <c r="AG135" s="29"/>
-      <c r="AH135" t="str">
+      <c r="AH135" s="29"/>
+      <c r="AI135" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2002, 2003, 2008, 2012, 2016, 2017, </v>
       </c>
     </row>
-    <row r="136" spans="1:34">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -35130,12 +35268,13 @@
       <c r="AE136" s="29"/>
       <c r="AF136" s="29"/>
       <c r="AG136" s="29"/>
-      <c r="AH136" t="str">
+      <c r="AH136" s="29"/>
+      <c r="AI136" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="137" spans="1:34">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -35228,12 +35367,13 @@
       <c r="AE137" s="29"/>
       <c r="AF137" s="29"/>
       <c r="AG137" s="29"/>
-      <c r="AH137" t="str">
+      <c r="AH137" s="29"/>
+      <c r="AI137" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="138" spans="1:34">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -35326,12 +35466,13 @@
       <c r="AE138" s="29"/>
       <c r="AF138" s="29"/>
       <c r="AG138" s="29"/>
-      <c r="AH138" t="str">
+      <c r="AH138" s="29"/>
+      <c r="AI138" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2018, </v>
       </c>
     </row>
-    <row r="139" spans="1:34">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -35424,12 +35565,13 @@
       <c r="AE139" s="29"/>
       <c r="AF139" s="29"/>
       <c r="AG139" s="29"/>
-      <c r="AH139" t="str">
+      <c r="AH139" s="29"/>
+      <c r="AI139" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2015, </v>
       </c>
     </row>
-    <row r="140" spans="1:34">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="e">
         <f>1+#REF!</f>
         <v>#REF!</v>
@@ -35522,12 +35664,13 @@
       <c r="AE140" s="29"/>
       <c r="AF140" s="29"/>
       <c r="AG140" s="29"/>
-      <c r="AH140" t="str">
+      <c r="AH140" s="29"/>
+      <c r="AI140" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, </v>
       </c>
     </row>
-    <row r="141" spans="1:34">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -35620,12 +35763,13 @@
       <c r="AE141" s="29"/>
       <c r="AF141" s="29"/>
       <c r="AG141" s="29"/>
-      <c r="AH141" t="str">
+      <c r="AH141" s="29"/>
+      <c r="AI141" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2007, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="142" spans="1:34">
+    <row r="142" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -35718,12 +35862,13 @@
       <c r="AE142" s="29"/>
       <c r="AF142" s="29"/>
       <c r="AG142" s="29"/>
-      <c r="AH142" t="str">
+      <c r="AH142" s="29"/>
+      <c r="AI142" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:34">
+    <row r="143" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -35816,12 +35961,13 @@
       <c r="AE143" s="29"/>
       <c r="AF143" s="29"/>
       <c r="AG143" s="29"/>
-      <c r="AH143" t="str">
+      <c r="AH143" s="29"/>
+      <c r="AI143" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2012, 2017, </v>
       </c>
     </row>
-    <row r="144" spans="1:34">
+    <row r="144" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -35914,12 +36060,13 @@
       <c r="AE144" s="29"/>
       <c r="AF144" s="29"/>
       <c r="AG144" s="29"/>
-      <c r="AH144" t="str">
+      <c r="AH144" s="29"/>
+      <c r="AI144" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="145" spans="1:80">
+    <row r="145" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -36012,12 +36159,13 @@
       <c r="AE145" s="29"/>
       <c r="AF145" s="29"/>
       <c r="AG145" s="29"/>
-      <c r="AH145" t="str">
+      <c r="AH145" s="29"/>
+      <c r="AI145" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2013, </v>
       </c>
     </row>
-    <row r="146" spans="1:80">
+    <row r="146" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -36110,12 +36258,13 @@
       <c r="AE146" s="29"/>
       <c r="AF146" s="29"/>
       <c r="AG146" s="29"/>
-      <c r="AH146" t="str">
+      <c r="AH146" s="29"/>
+      <c r="AI146" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
     </row>
-    <row r="147" spans="1:80">
+    <row r="147" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -36208,12 +36357,13 @@
       <c r="AE147" s="29"/>
       <c r="AF147" s="29"/>
       <c r="AG147" s="29"/>
-      <c r="AH147" t="str">
+      <c r="AH147" s="29"/>
+      <c r="AI147" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2005, 2008, 2012, 2014, 2017, 2018, </v>
       </c>
     </row>
-    <row r="148" spans="1:80">
+    <row r="148" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
@@ -36306,12 +36456,13 @@
       <c r="AE148" s="53"/>
       <c r="AF148" s="53"/>
       <c r="AG148" s="53"/>
-      <c r="AH148" t="str">
+      <c r="AH148" s="53"/>
+      <c r="AI148" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2004, 2011, 2014, 2019, </v>
       </c>
     </row>
-    <row r="149" spans="1:80">
+    <row r="149" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B149" s="5">
         <v>146</v>
       </c>
@@ -36400,16 +36551,17 @@
       <c r="AE149" s="55"/>
       <c r="AF149" s="55"/>
       <c r="AG149" s="55"/>
-      <c r="AH149" t="str">
+      <c r="AH149" s="55"/>
+      <c r="AI149" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2004, 2013, </v>
       </c>
-      <c r="AI149" s="32"/>
-      <c r="AJ149" s="33" t="s">
+      <c r="AJ149" s="32"/>
+      <c r="AK149" s="33" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="150" spans="1:80">
+    <row r="150" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B150" s="5">
         <v>147</v>
       </c>
@@ -36498,16 +36650,17 @@
       <c r="AE150" s="55"/>
       <c r="AF150" s="55"/>
       <c r="AG150" s="55"/>
-      <c r="AH150" t="str">
+      <c r="AH150" s="55"/>
+      <c r="AI150" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2019, </v>
       </c>
-      <c r="AI150" s="32"/>
-      <c r="AJ150" s="37" t="s">
+      <c r="AJ150" s="32"/>
+      <c r="AK150" s="37" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="151" spans="1:80">
+    <row r="151" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B151" s="5">
         <v>148</v>
       </c>
@@ -36600,18 +36753,19 @@
       </c>
       <c r="AF151" s="20"/>
       <c r="AG151" s="20"/>
-      <c r="AH151" t="str">
+      <c r="AH151" s="20"/>
+      <c r="AI151" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
-      <c r="AI151" s="32" t="s">
+      <c r="AJ151" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="AJ151" s="32" t="s">
+      <c r="AK151" s="32" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="152" spans="1:80">
+    <row r="152" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B152" s="5">
         <v>149</v>
       </c>
@@ -36704,18 +36858,19 @@
       </c>
       <c r="AF152" s="56"/>
       <c r="AG152" s="56"/>
-      <c r="AH152" t="str">
+      <c r="AH152" s="56"/>
+      <c r="AI152" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
-      <c r="AI152" s="32" t="s">
+      <c r="AJ152" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="AJ152" s="37" t="s">
+      <c r="AK152" s="37" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="153" spans="1:80">
+    <row r="153" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B153" s="5">
         <v>150</v>
       </c>
@@ -36808,19 +36963,20 @@
       </c>
       <c r="AF153" s="56"/>
       <c r="AG153" s="56"/>
-      <c r="AH153" t="str">
+      <c r="AH153" s="56"/>
+      <c r="AI153" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
-      <c r="AI153" s="32"/>
-      <c r="AJ153" s="33" t="s">
+      <c r="AJ153" s="32"/>
+      <c r="AK153" s="33" t="s">
         <v>381</v>
       </c>
-      <c r="AK153" s="29" t="s">
+      <c r="AL153" s="29" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="154" spans="1:80">
+    <row r="154" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B154" s="5">
         <v>151</v>
       </c>
@@ -36913,16 +37069,17 @@
       </c>
       <c r="AF154" s="57"/>
       <c r="AG154" s="57"/>
-      <c r="AH154" t="str">
+      <c r="AH154" s="57"/>
+      <c r="AI154" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
-      <c r="AI154" s="32" t="s">
+      <c r="AJ154" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="AJ154" s="32"/>
+      <c r="AK154" s="32"/>
     </row>
-    <row r="155" spans="1:80">
+    <row r="155" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B155" s="5">
         <v>152</v>
       </c>
@@ -37015,18 +37172,19 @@
       </c>
       <c r="AF155" s="19"/>
       <c r="AG155" s="19"/>
-      <c r="AH155" t="str">
+      <c r="AH155" s="19"/>
+      <c r="AI155" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
-      <c r="AI155" s="32" t="s">
+      <c r="AJ155" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="AJ155" s="32" t="s">
+      <c r="AK155" s="32" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="156" spans="1:80">
+    <row r="156" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B156" s="5">
         <v>153</v>
       </c>
@@ -37115,14 +37273,15 @@
       <c r="AE156" s="55"/>
       <c r="AF156" s="55"/>
       <c r="AG156" s="55"/>
-      <c r="AH156" t="str">
+      <c r="AH156" s="55"/>
+      <c r="AI156" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AI156" s="32"/>
       <c r="AJ156" s="32"/>
+      <c r="AK156" s="32"/>
     </row>
-    <row r="157" spans="1:80">
+    <row r="157" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B157" s="5">
         <v>154</v>
       </c>
@@ -37211,16 +37370,17 @@
       <c r="AE157" s="56"/>
       <c r="AF157" s="56"/>
       <c r="AG157" s="56"/>
-      <c r="AH157" t="str">
+      <c r="AH157" s="56"/>
+      <c r="AI157" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, </v>
       </c>
-      <c r="AI157" s="32"/>
-      <c r="AJ157" s="37" t="s">
+      <c r="AJ157" s="32"/>
+      <c r="AK157" s="37" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="158" spans="1:80">
+    <row r="158" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B158" s="5">
         <v>155</v>
       </c>
@@ -37313,18 +37473,19 @@
       </c>
       <c r="AF158" s="56"/>
       <c r="AG158" s="56"/>
-      <c r="AH158" t="str">
+      <c r="AH158" s="56"/>
+      <c r="AI158" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
       </c>
-      <c r="AI158" s="32" t="s">
+      <c r="AJ158" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="AJ158" s="37" t="s">
+      <c r="AK158" s="37" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="159" spans="1:80">
+    <row r="159" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B159" s="5">
         <v>156</v>
       </c>
@@ -37415,23 +37576,30 @@
       <c r="AE159" s="30">
         <v>1</v>
       </c>
-      <c r="AF159" s="39"/>
-      <c r="AG159" s="39"/>
-      <c r="AH159" t="str">
+      <c r="AF159" s="39">
+        <v>1</v>
+      </c>
+      <c r="AG159" s="39">
+        <v>1</v>
+      </c>
+      <c r="AH159" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI159" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
-      </c>
-      <c r="AI159" s="39"/>
-      <c r="AJ159" s="41" t="s">
+        <v xml:space="preserve">2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AJ159" s="39"/>
+      <c r="AK159" s="41" t="s">
         <v>392</v>
       </c>
-      <c r="AK159" t="s">
+      <c r="AL159" t="s">
         <v>392</v>
       </c>
-      <c r="AL159"/>
-      <c r="CB159" s="29"/>
+      <c r="AM159"/>
+      <c r="CC159" s="29"/>
     </row>
-    <row r="160" spans="1:80">
+    <row r="160" spans="1:81" x14ac:dyDescent="0.2">
       <c r="B160" s="5">
         <v>157</v>
       </c>
@@ -37522,21 +37690,22 @@
       </c>
       <c r="AF160" s="58"/>
       <c r="AG160" s="39"/>
-      <c r="AH160" t="str">
+      <c r="AH160" s="39"/>
+      <c r="AI160" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2017, 2018, 2019, 2022, </v>
       </c>
-      <c r="AI160" s="41" t="s">
+      <c r="AJ160" s="41" t="s">
         <v>394</v>
       </c>
-      <c r="AJ160" s="39"/>
-      <c r="AK160" t="s">
+      <c r="AK160" s="39"/>
+      <c r="AL160" t="s">
         <v>395</v>
       </c>
-      <c r="AL160"/>
-      <c r="CB160" s="29"/>
+      <c r="AM160"/>
+      <c r="CC160" s="29"/>
     </row>
-    <row r="161" spans="2:80">
+    <row r="161" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B161" s="5">
         <v>158</v>
       </c>
@@ -37631,21 +37800,24 @@
       <c r="AG161" s="39">
         <v>1</v>
       </c>
-      <c r="AH161" t="str">
+      <c r="AH161" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI161" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI161" s="39"/>
-      <c r="AJ161" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ161" s="39"/>
+      <c r="AK161" s="41" t="s">
         <v>397</v>
       </c>
-      <c r="AK161" t="s">
+      <c r="AL161" t="s">
         <v>398</v>
       </c>
-      <c r="AL161"/>
-      <c r="CB161" s="29"/>
+      <c r="AM161"/>
+      <c r="CC161" s="29"/>
     </row>
-    <row r="162" spans="2:80">
+    <row r="162" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B162" s="5">
         <v>159</v>
       </c>
@@ -37742,23 +37914,26 @@
       <c r="AG162" s="39">
         <v>1</v>
       </c>
-      <c r="AH162" t="str">
-        <f>+IF($E162=1,RIGHT(E$3,4)&amp;", ","")&amp;IF($F162=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G162=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H162=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I162=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J162=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K162=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L162=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M162=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N162=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O162=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P162=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q162=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R162=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S162=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T162=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U162=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V162=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W162=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X162=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y162=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z162=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA162=1, RIGHT(AA$3,4)&amp;", ", "")&amp;IF($AB162=1, RIGHT(AB$3,4)&amp;", ", "")&amp;IF($AC162=1, RIGHT(AC$3,4)&amp;", ", "")&amp;IF($AD162=1, RIGHT(AD$3,4)&amp;", ", "")&amp;IF($AE162=1, RIGHT(AE$3,4)&amp;", ", "")&amp;IF($AF162=1, RIGHT(AF$3,4)&amp;", ", "")&amp;IF($AG162=1, RIGHT(AG$3,4)&amp;", ", "")</f>
-        <v xml:space="preserve">2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
-      </c>
-      <c r="AI162" s="41" t="s">
+      <c r="AH162" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI162" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AJ162" s="41" t="s">
         <v>400</v>
       </c>
-      <c r="AJ162" s="41" t="s">
+      <c r="AK162" s="41" t="s">
         <v>401</v>
       </c>
-      <c r="AK162" s="40" t="s">
+      <c r="AL162" s="40" t="s">
         <v>402</v>
       </c>
-      <c r="AL162"/>
-      <c r="CB162" s="29"/>
+      <c r="AM162"/>
+      <c r="CC162" s="29"/>
     </row>
-    <row r="163" spans="2:80">
+    <row r="163" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B163" s="5">
         <v>160</v>
       </c>
@@ -37851,23 +38026,26 @@
       </c>
       <c r="AF163" s="39"/>
       <c r="AG163" s="39"/>
-      <c r="AH163" t="str">
+      <c r="AH163" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI163" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
-      </c>
-      <c r="AI163" s="39"/>
-      <c r="AJ163" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2025, </v>
+      </c>
+      <c r="AJ163" s="39"/>
+      <c r="AK163" s="41" t="s">
         <v>404</v>
       </c>
-      <c r="AK163" s="40" t="s">
+      <c r="AL163" s="40" t="s">
         <v>405</v>
       </c>
-      <c r="AL163" s="40" t="s">
+      <c r="AM163" s="40" t="s">
         <v>406</v>
       </c>
-      <c r="CB163" s="29"/>
+      <c r="CC163" s="29"/>
     </row>
-    <row r="164" spans="2:80">
+    <row r="164" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B164" s="5">
         <v>161</v>
       </c>
@@ -37958,19 +38136,22 @@
       <c r="AG164" s="39">
         <v>1</v>
       </c>
-      <c r="AH164" t="str">
+      <c r="AH164" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI164" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">2016, 2017, 2018, 2019, 2024, </v>
-      </c>
-      <c r="AI164" s="39"/>
-      <c r="AJ164" s="41" t="s">
+        <v xml:space="preserve">2016, 2017, 2018, 2019, 2024, 2025, </v>
+      </c>
+      <c r="AJ164" s="39"/>
+      <c r="AK164" s="41" t="s">
         <v>408</v>
       </c>
-      <c r="AK164"/>
       <c r="AL164"/>
-      <c r="CB164" s="29"/>
+      <c r="AM164"/>
+      <c r="CC164" s="29"/>
     </row>
-    <row r="165" spans="2:80" ht="14.25" customHeight="1">
+    <row r="165" spans="2:81" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B165" s="5">
         <v>162</v>
       </c>
@@ -38063,23 +38244,26 @@
         <v>1</v>
       </c>
       <c r="AG165" s="39"/>
-      <c r="AH165" t="str">
+      <c r="AH165" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI165" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">2008, 2014, 2017, 2018, 2019, 2022, 2023, </v>
-      </c>
-      <c r="AI165" s="41" t="s">
+        <v xml:space="preserve">2008, 2014, 2017, 2018, 2019, 2022, 2023, 2025, </v>
+      </c>
+      <c r="AJ165" s="41" t="s">
         <v>410</v>
       </c>
-      <c r="AJ165" s="39" t="s">
+      <c r="AK165" s="39" t="s">
         <v>411</v>
       </c>
-      <c r="AK165" s="40" t="s">
+      <c r="AL165" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="AL165"/>
-      <c r="CB165" s="29"/>
+      <c r="AM165"/>
+      <c r="CC165" s="29"/>
     </row>
-    <row r="166" spans="2:80">
+    <row r="166" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B166" s="5">
         <v>163</v>
       </c>
@@ -38176,21 +38360,24 @@
       <c r="AG166" s="56">
         <v>1</v>
       </c>
-      <c r="AH166" t="str">
+      <c r="AH166" s="56">
+        <v>1</v>
+      </c>
+      <c r="AI166" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
-      </c>
-      <c r="AI166" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AJ166" s="41" t="s">
         <v>414</v>
       </c>
-      <c r="AJ166" s="41" t="s">
+      <c r="AK166" s="41" t="s">
         <v>415</v>
       </c>
-      <c r="AK166"/>
       <c r="AL166"/>
-      <c r="CB166" s="29"/>
+      <c r="AM166"/>
+      <c r="CC166" s="29"/>
     </row>
-    <row r="167" spans="2:80">
+    <row r="167" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B167" s="5">
         <v>164</v>
       </c>
@@ -38285,21 +38472,24 @@
       <c r="AG167" s="39">
         <v>1</v>
       </c>
-      <c r="AH167" t="str">
+      <c r="AH167" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI167" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI167" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ167" s="41" t="s">
         <v>417</v>
       </c>
-      <c r="AJ167" s="39" t="s">
+      <c r="AK167" s="39" t="s">
         <v>418</v>
       </c>
-      <c r="AK167"/>
       <c r="AL167"/>
-      <c r="CB167" s="29"/>
+      <c r="AM167"/>
+      <c r="CC167" s="29"/>
     </row>
-    <row r="168" spans="2:80">
+    <row r="168" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B168" s="5">
         <v>165</v>
       </c>
@@ -38392,19 +38582,22 @@
       </c>
       <c r="AF168" s="39"/>
       <c r="AG168" s="39"/>
-      <c r="AH168" t="str">
+      <c r="AH168" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI168" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
-      </c>
-      <c r="AI168" s="39"/>
-      <c r="AJ168" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2025, </v>
+      </c>
+      <c r="AJ168" s="39"/>
+      <c r="AK168" s="41" t="s">
         <v>420</v>
       </c>
-      <c r="AK168"/>
       <c r="AL168"/>
-      <c r="CB168" s="29"/>
+      <c r="AM168"/>
+      <c r="CC168" s="29"/>
     </row>
-    <row r="169" spans="2:80">
+    <row r="169" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B169" s="5">
         <v>166</v>
       </c>
@@ -38499,26 +38692,29 @@
       <c r="AG169" s="39">
         <v>1</v>
       </c>
-      <c r="AH169" t="str">
+      <c r="AH169" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI169" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI169" s="39"/>
-      <c r="AJ169" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ169" s="39"/>
+      <c r="AK169" s="41" t="s">
         <v>422</v>
       </c>
-      <c r="AK169" s="40" t="s">
+      <c r="AL169" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="AL169" s="40" t="s">
+      <c r="AM169" s="40" t="s">
         <v>424</v>
       </c>
-      <c r="AM169" s="29" t="s">
+      <c r="AN169" s="29" t="s">
         <v>425</v>
       </c>
-      <c r="CB169" s="29"/>
+      <c r="CC169" s="29"/>
     </row>
-    <row r="170" spans="2:80">
+    <row r="170" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B170" s="5">
         <v>167</v>
       </c>
@@ -38613,21 +38809,24 @@
       <c r="AG170" s="56">
         <v>1</v>
       </c>
-      <c r="AH170" t="str">
+      <c r="AH170" s="56">
+        <v>1</v>
+      </c>
+      <c r="AI170" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI170" s="39"/>
-      <c r="AJ170" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ170" s="39"/>
+      <c r="AK170" s="41" t="s">
         <v>427</v>
       </c>
-      <c r="AK170" s="40" t="s">
+      <c r="AL170" s="40" t="s">
         <v>428</v>
       </c>
-      <c r="AL170"/>
-      <c r="CB170" s="29"/>
+      <c r="AM170"/>
+      <c r="CC170" s="29"/>
     </row>
-    <row r="171" spans="2:80">
+    <row r="171" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B171" s="5">
         <v>168</v>
       </c>
@@ -38722,25 +38921,28 @@
       <c r="AG171" s="39">
         <v>1</v>
       </c>
-      <c r="AH171" t="str">
+      <c r="AH171" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI171" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI171" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ171" s="41" t="s">
         <v>430</v>
       </c>
-      <c r="AJ171" s="41" t="s">
+      <c r="AK171" s="41" t="s">
         <v>431</v>
       </c>
-      <c r="AK171" t="s">
+      <c r="AL171" t="s">
         <v>432</v>
       </c>
-      <c r="AL171" t="s">
+      <c r="AM171" t="s">
         <v>425</v>
       </c>
-      <c r="CB171" s="29"/>
+      <c r="CC171" s="29"/>
     </row>
-    <row r="172" spans="2:80">
+    <row r="172" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B172" s="5">
         <v>169</v>
       </c>
@@ -38835,25 +39037,28 @@
       <c r="AG172" s="39">
         <v>1</v>
       </c>
-      <c r="AH172" t="str">
+      <c r="AH172" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI172" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI172" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ172" s="41" t="s">
         <v>434</v>
       </c>
-      <c r="AJ172" s="41" t="s">
+      <c r="AK172" s="41" t="s">
         <v>435</v>
       </c>
-      <c r="AK172" s="40" t="s">
+      <c r="AL172" s="40" t="s">
         <v>436</v>
       </c>
-      <c r="AL172" s="40" t="s">
+      <c r="AM172" s="40" t="s">
         <v>437</v>
       </c>
-      <c r="CB172" s="29"/>
+      <c r="CC172" s="29"/>
     </row>
-    <row r="173" spans="2:80">
+    <row r="173" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B173" s="5">
         <v>170</v>
       </c>
@@ -38946,23 +39151,26 @@
       </c>
       <c r="AF173" s="56"/>
       <c r="AG173" s="56"/>
-      <c r="AH173" t="str">
+      <c r="AH173" s="56">
+        <v>1</v>
+      </c>
+      <c r="AI173" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
-      </c>
-      <c r="AI173" s="39"/>
-      <c r="AJ173" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2025, </v>
+      </c>
+      <c r="AJ173" s="39"/>
+      <c r="AK173" s="41" t="s">
         <v>439</v>
       </c>
-      <c r="AK173" t="s">
+      <c r="AL173" t="s">
         <v>440</v>
       </c>
-      <c r="AL173" t="s">
+      <c r="AM173" t="s">
         <v>441</v>
       </c>
-      <c r="CB173" s="29"/>
+      <c r="CC173" s="29"/>
     </row>
-    <row r="174" spans="2:80">
+    <row r="174" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B174" s="5">
         <v>171</v>
       </c>
@@ -39055,21 +39263,24 @@
       </c>
       <c r="AF174" s="56"/>
       <c r="AG174" s="56"/>
-      <c r="AH174" t="str">
+      <c r="AH174" s="56">
+        <v>1</v>
+      </c>
+      <c r="AI174" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, </v>
-      </c>
-      <c r="AI174" s="39" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2025, </v>
+      </c>
+      <c r="AJ174" s="39" t="s">
         <v>443</v>
       </c>
-      <c r="AJ174" s="41" t="s">
+      <c r="AK174" s="41" t="s">
         <v>444</v>
       </c>
-      <c r="AK174"/>
       <c r="AL174"/>
-      <c r="CB174" s="29"/>
+      <c r="AM174"/>
+      <c r="CC174" s="29"/>
     </row>
-    <row r="175" spans="2:80">
+    <row r="175" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B175" s="5">
         <v>172</v>
       </c>
@@ -39166,23 +39377,26 @@
       <c r="AG175" s="39">
         <v>1</v>
       </c>
-      <c r="AH175" t="str">
+      <c r="AH175" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI175" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
-      </c>
-      <c r="AI175" s="39" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AJ175" s="39" t="s">
         <v>446</v>
       </c>
-      <c r="AJ175" s="41" t="s">
+      <c r="AK175" s="41" t="s">
         <v>447</v>
       </c>
-      <c r="AK175" t="s">
+      <c r="AL175" t="s">
         <v>448</v>
       </c>
-      <c r="AL175"/>
-      <c r="CB175" s="29"/>
+      <c r="AM175"/>
+      <c r="CC175" s="29"/>
     </row>
-    <row r="176" spans="2:80">
+    <row r="176" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B176" s="5">
         <v>173</v>
       </c>
@@ -39277,21 +39491,24 @@
       <c r="AG176" s="39">
         <v>1</v>
       </c>
-      <c r="AH176" t="str">
+      <c r="AH176" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI176" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI176" s="39" t="s">
+        <v xml:space="preserve">1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ176" s="39" t="s">
         <v>450</v>
       </c>
-      <c r="AJ176" s="39" t="s">
+      <c r="AK176" s="39" t="s">
         <v>451</v>
       </c>
-      <c r="AK176"/>
       <c r="AL176"/>
-      <c r="CB176" s="29"/>
+      <c r="AM176"/>
+      <c r="CC176" s="29"/>
     </row>
-    <row r="177" spans="2:80">
+    <row r="177" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B177" s="5">
         <v>174</v>
       </c>
@@ -39386,21 +39603,24 @@
       <c r="AG177" s="56">
         <v>1</v>
       </c>
-      <c r="AH177" t="str">
+      <c r="AH177" s="56">
+        <v>1</v>
+      </c>
+      <c r="AI177" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI177" s="39"/>
-      <c r="AJ177" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ177" s="39"/>
+      <c r="AK177" s="41" t="s">
         <v>453</v>
       </c>
-      <c r="AK177" t="s">
+      <c r="AL177" t="s">
         <v>454</v>
       </c>
-      <c r="AL177"/>
-      <c r="CB177" s="29"/>
+      <c r="AM177"/>
+      <c r="CC177" s="29"/>
     </row>
-    <row r="178" spans="2:80">
+    <row r="178" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B178" s="5">
         <v>175</v>
       </c>
@@ -39495,21 +39715,24 @@
       <c r="AG178" s="56">
         <v>1</v>
       </c>
-      <c r="AH178" t="str">
+      <c r="AH178" s="56">
+        <v>1</v>
+      </c>
+      <c r="AI178" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI178" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ178" s="41" t="s">
         <v>456</v>
       </c>
-      <c r="AJ178" s="41" t="s">
+      <c r="AK178" s="41" t="s">
         <v>457</v>
       </c>
-      <c r="AK178"/>
       <c r="AL178"/>
-      <c r="CB178" s="29"/>
+      <c r="AM178"/>
+      <c r="CC178" s="29"/>
     </row>
-    <row r="179" spans="2:80">
+    <row r="179" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B179" s="5">
         <v>176</v>
       </c>
@@ -39604,23 +39827,26 @@
       <c r="AG179" s="39">
         <v>1</v>
       </c>
-      <c r="AH179" t="str">
+      <c r="AH179" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI179" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI179" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ179" s="41" t="s">
         <v>459</v>
       </c>
-      <c r="AJ179" s="41" t="s">
+      <c r="AK179" s="41" t="s">
         <v>460</v>
       </c>
-      <c r="AK179" t="s">
+      <c r="AL179" t="s">
         <v>461</v>
       </c>
-      <c r="AL179"/>
-      <c r="CB179" s="29"/>
+      <c r="AM179"/>
+      <c r="CC179" s="29"/>
     </row>
-    <row r="180" spans="2:80">
+    <row r="180" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B180" s="5">
         <v>177</v>
       </c>
@@ -39717,23 +39943,26 @@
       <c r="AG180" s="39">
         <v>1</v>
       </c>
-      <c r="AH180" t="str">
+      <c r="AH180" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI180" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
-      </c>
-      <c r="AI180" s="39"/>
-      <c r="AJ180" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AJ180" s="39"/>
+      <c r="AK180" s="41" t="s">
         <v>463</v>
       </c>
-      <c r="AK180" t="s">
+      <c r="AL180" t="s">
         <v>464</v>
       </c>
-      <c r="AL180" s="40" t="s">
+      <c r="AM180" s="40" t="s">
         <v>465</v>
       </c>
-      <c r="CB180" s="29"/>
+      <c r="CC180" s="29"/>
     </row>
-    <row r="181" spans="2:80">
+    <row r="181" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B181" s="5">
         <v>178</v>
       </c>
@@ -39830,25 +40059,28 @@
       <c r="AG181" s="39">
         <v>1</v>
       </c>
-      <c r="AH181" t="str">
+      <c r="AH181" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI181" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
-      </c>
-      <c r="AI181" s="39" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AJ181" s="39" t="s">
         <v>467</v>
       </c>
-      <c r="AJ181" s="41" t="s">
+      <c r="AK181" s="41" t="s">
         <v>468</v>
       </c>
-      <c r="AK181" t="s">
+      <c r="AL181" t="s">
         <v>469</v>
       </c>
-      <c r="AL181" t="s">
+      <c r="AM181" t="s">
         <v>470</v>
       </c>
-      <c r="CB181" s="29"/>
+      <c r="CC181" s="29"/>
     </row>
-    <row r="182" spans="2:80">
+    <row r="182" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B182" s="5">
         <v>179</v>
       </c>
@@ -39937,19 +40169,20 @@
       <c r="AE182" s="39"/>
       <c r="AF182" s="39"/>
       <c r="AG182" s="39"/>
-      <c r="AH182" t="str">
+      <c r="AH182" s="39"/>
+      <c r="AI182" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2008, 2014, 2015, 2016, </v>
       </c>
-      <c r="AI182" s="39"/>
-      <c r="AJ182" s="41" t="s">
+      <c r="AJ182" s="39"/>
+      <c r="AK182" s="41" t="s">
         <v>472</v>
       </c>
-      <c r="AK182"/>
       <c r="AL182"/>
-      <c r="CB182" s="29"/>
+      <c r="AM182"/>
+      <c r="CC182" s="29"/>
     </row>
-    <row r="183" spans="2:80">
+    <row r="183" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B183" s="5">
         <v>180</v>
       </c>
@@ -40044,23 +40277,26 @@
       <c r="AG183" s="39">
         <v>1</v>
       </c>
-      <c r="AH183" t="str">
+      <c r="AH183" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI183" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI183" s="39"/>
-      <c r="AJ183" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ183" s="39"/>
+      <c r="AK183" s="41" t="s">
         <v>474</v>
       </c>
-      <c r="AK183" s="41" t="s">
+      <c r="AL183" s="41" t="s">
         <v>475</v>
       </c>
-      <c r="AL183" t="s">
+      <c r="AM183" t="s">
         <v>425</v>
       </c>
-      <c r="CB183" s="29"/>
+      <c r="CC183" s="29"/>
     </row>
-    <row r="184" spans="2:80">
+    <row r="184" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B184" s="5">
         <v>181</v>
       </c>
@@ -40155,26 +40391,29 @@
       <c r="AG184" s="39">
         <v>1</v>
       </c>
-      <c r="AH184" t="str">
+      <c r="AH184" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI184" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI184" s="39"/>
-      <c r="AJ184" s="41" t="s">
+        <v xml:space="preserve">1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ184" s="39"/>
+      <c r="AK184" s="41" t="s">
         <v>477</v>
       </c>
-      <c r="AK184" s="40" t="s">
+      <c r="AL184" s="40" t="s">
         <v>478</v>
       </c>
-      <c r="AL184" t="s">
+      <c r="AM184" t="s">
         <v>479</v>
       </c>
-      <c r="AM184" s="29" t="s">
+      <c r="AN184" s="29" t="s">
         <v>425</v>
       </c>
-      <c r="CB184" s="29"/>
+      <c r="CC184" s="29"/>
     </row>
-    <row r="185" spans="2:80">
+    <row r="185" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B185" s="5">
         <v>182</v>
       </c>
@@ -40269,25 +40508,28 @@
       <c r="AG185" s="39">
         <v>1</v>
       </c>
-      <c r="AH185" t="str">
+      <c r="AH185" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI185" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI185" s="39" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ185" s="39" t="s">
         <v>481</v>
       </c>
-      <c r="AJ185" s="41" t="s">
+      <c r="AK185" s="41" t="s">
         <v>482</v>
       </c>
-      <c r="AK185" s="40" t="s">
+      <c r="AL185" s="40" t="s">
         <v>483</v>
       </c>
-      <c r="AL185" s="40" t="s">
+      <c r="AM185" s="40" t="s">
         <v>425</v>
       </c>
-      <c r="CB185" s="29"/>
+      <c r="CC185" s="29"/>
     </row>
-    <row r="186" spans="2:80">
+    <row r="186" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B186" s="5">
         <v>183</v>
       </c>
@@ -40382,21 +40624,24 @@
       <c r="AG186" s="56">
         <v>1</v>
       </c>
-      <c r="AH186" t="str">
+      <c r="AH186" s="56">
+        <v>1</v>
+      </c>
+      <c r="AI186" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI186" s="39"/>
-      <c r="AJ186" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ186" s="39"/>
+      <c r="AK186" s="41" t="s">
         <v>485</v>
       </c>
-      <c r="AK186" t="s">
+      <c r="AL186" t="s">
         <v>486</v>
       </c>
-      <c r="AL186"/>
-      <c r="CB186" s="29"/>
+      <c r="AM186"/>
+      <c r="CC186" s="29"/>
     </row>
-    <row r="187" spans="2:80">
+    <row r="187" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B187" s="5">
         <v>184</v>
       </c>
@@ -40491,21 +40736,24 @@
       <c r="AG187" s="39">
         <v>1</v>
       </c>
-      <c r="AH187" t="str">
+      <c r="AH187" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI187" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI187" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ187" s="41" t="s">
         <v>488</v>
       </c>
-      <c r="AJ187" s="41" t="s">
+      <c r="AK187" s="41" t="s">
         <v>489</v>
       </c>
-      <c r="AK187"/>
       <c r="AL187"/>
-      <c r="CB187" s="29"/>
+      <c r="AM187"/>
+      <c r="CC187" s="29"/>
     </row>
-    <row r="188" spans="2:80">
+    <row r="188" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B188" s="5">
         <v>185</v>
       </c>
@@ -40600,23 +40848,26 @@
       <c r="AG188" s="39">
         <v>1</v>
       </c>
-      <c r="AH188" t="str">
+      <c r="AH188" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI188" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI188" s="39" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ188" s="39" t="s">
         <v>491</v>
       </c>
-      <c r="AJ188" s="41" t="s">
+      <c r="AK188" s="41" t="s">
         <v>492</v>
       </c>
-      <c r="AK188" t="s">
+      <c r="AL188" t="s">
         <v>425</v>
       </c>
-      <c r="AL188"/>
-      <c r="CB188" s="29"/>
+      <c r="AM188"/>
+      <c r="CC188" s="29"/>
     </row>
-    <row r="189" spans="2:80">
+    <row r="189" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B189" s="5">
         <v>186</v>
       </c>
@@ -40707,19 +40958,20 @@
       <c r="AG189" s="56">
         <v>1</v>
       </c>
-      <c r="AH189" t="str">
+      <c r="AH189" s="56"/>
+      <c r="AI189" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2024, </v>
       </c>
-      <c r="AI189" s="39"/>
-      <c r="AJ189" s="41" t="s">
+      <c r="AJ189" s="39"/>
+      <c r="AK189" s="41" t="s">
         <v>494</v>
       </c>
-      <c r="AK189"/>
       <c r="AL189"/>
-      <c r="CB189" s="29"/>
+      <c r="AM189"/>
+      <c r="CC189" s="29"/>
     </row>
-    <row r="190" spans="2:80">
+    <row r="190" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B190" s="5">
         <v>187</v>
       </c>
@@ -40816,23 +41068,26 @@
       <c r="AG190" s="56">
         <v>1</v>
       </c>
-      <c r="AH190" t="str">
+      <c r="AH190" s="56">
+        <v>1</v>
+      </c>
+      <c r="AI190" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
-      </c>
-      <c r="AI190" s="39"/>
-      <c r="AJ190" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AJ190" s="39"/>
+      <c r="AK190" s="41" t="s">
         <v>496</v>
       </c>
-      <c r="AK190" t="s">
+      <c r="AL190" t="s">
         <v>497</v>
       </c>
-      <c r="AL190" s="29" t="s">
+      <c r="AM190" s="29" t="s">
         <v>496</v>
       </c>
-      <c r="CB190" s="29"/>
+      <c r="CC190" s="29"/>
     </row>
-    <row r="191" spans="2:80">
+    <row r="191" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B191" s="5">
         <v>188</v>
       </c>
@@ -40927,21 +41182,22 @@
       <c r="AG191" s="39">
         <v>1</v>
       </c>
-      <c r="AH191" t="str">
+      <c r="AH191" s="39"/>
+      <c r="AI191" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
       </c>
-      <c r="AI191" s="39"/>
-      <c r="AJ191" s="41" t="s">
+      <c r="AJ191" s="39"/>
+      <c r="AK191" s="41" t="s">
         <v>499</v>
       </c>
-      <c r="AK191" t="s">
+      <c r="AL191" t="s">
         <v>425</v>
       </c>
-      <c r="AL191"/>
-      <c r="CB191" s="29"/>
+      <c r="AM191"/>
+      <c r="CC191" s="29"/>
     </row>
-    <row r="192" spans="2:80">
+    <row r="192" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B192" s="5">
         <v>189</v>
       </c>
@@ -41036,19 +41292,22 @@
       <c r="AG192" s="39">
         <v>1</v>
       </c>
-      <c r="AH192" t="str">
+      <c r="AH192" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI192" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, </v>
-      </c>
-      <c r="AI192" s="39"/>
-      <c r="AJ192" s="41" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2024, 2025, </v>
+      </c>
+      <c r="AJ192" s="39"/>
+      <c r="AK192" s="41" t="s">
         <v>501</v>
       </c>
-      <c r="AK192"/>
       <c r="AL192"/>
-      <c r="CB192" s="29"/>
+      <c r="AM192"/>
+      <c r="CC192" s="29"/>
     </row>
-    <row r="193" spans="2:80">
+    <row r="193" spans="2:81" x14ac:dyDescent="0.2">
       <c r="B193" s="5">
         <v>190</v>
       </c>
@@ -41145,110 +41404,96 @@
       <c r="AG193" s="39">
         <v>1</v>
       </c>
-      <c r="AH193" t="str">
+      <c r="AH193" s="39">
+        <v>1</v>
+      </c>
+      <c r="AI193" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
-      </c>
-      <c r="AI193" s="39" t="s">
+        <v xml:space="preserve">1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
+      </c>
+      <c r="AJ193" s="39" t="s">
         <v>503</v>
       </c>
-      <c r="AJ193" s="41" t="s">
+      <c r="AK193" s="41" t="s">
         <v>504</v>
       </c>
-      <c r="AK193"/>
       <c r="AL193"/>
-      <c r="CB193" s="29"/>
+      <c r="AM193"/>
+      <c r="CC193" s="29"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AJ149" r:id="rId1" display="https://www.iga.gov.bh/en/category/reports" xr:uid="{13FBE199-AF70-4FE6-B8A7-6B7D021EE558}"/>
-    <hyperlink ref="AJ152" r:id="rId2" xr:uid="{B0B6E57C-09A4-4659-82A6-7C5C121A772E}"/>
-    <hyperlink ref="AJ153" r:id="rId3" display="http://www.ksh.hu/data_access_safe_centre_access" xr:uid="{FA610065-907B-43A9-BDD4-497A2152D63F}"/>
-    <hyperlink ref="AL163" r:id="rId4" xr:uid="{C0B8B1D7-F697-44E9-950D-0C5A3FBCF76C}"/>
-    <hyperlink ref="AI178" r:id="rId5" location="_r=&amp;collection=&amp;country=107&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{6C3F1886-6624-4E04-A741-ED3366339968}"/>
-    <hyperlink ref="AJ183" r:id="rId6" xr:uid="{5C9BBBFC-7A8C-4EC5-A0CF-C973CFD44550}"/>
-    <hyperlink ref="AK183" r:id="rId7" xr:uid="{B7E3C743-7B39-4D86-9472-8BD2AC324C56}"/>
-    <hyperlink ref="AJ157" r:id="rId8" xr:uid="{9094FBC3-21C3-4A32-A7EE-1C38ADE67FA0}"/>
-    <hyperlink ref="AJ158" r:id="rId9" location="!/view/en/VBD_SLOVSTAT/pr2018rs/v_pr2018rs_00_00_00_en" xr:uid="{3C3D633D-E51A-48F2-BE9B-B922A980143C}"/>
-    <hyperlink ref="AJ159" r:id="rId10" xr:uid="{4806463F-8D0B-4680-AADD-8AA89830D05E}"/>
-    <hyperlink ref="AI160" r:id="rId11" location="_r=&amp;collection=&amp;country=216&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{4E6F976A-EA20-4694-844D-FA9EEC07C251}"/>
-    <hyperlink ref="AJ161" r:id="rId12" xr:uid="{BD4A16C7-AB46-4E49-9D5A-898FCC37723A}"/>
-    <hyperlink ref="AJ163" r:id="rId13" xr:uid="{16FD7C52-64A2-41E0-8D08-E0D0F7EF17C9}"/>
-    <hyperlink ref="AK163" r:id="rId14" location="figures" xr:uid="{832B8C73-1423-4F9E-955F-82089634F0C4}"/>
-    <hyperlink ref="AJ166" r:id="rId15" xr:uid="{FA867C7F-7376-4FF1-B16C-3853F9D287BD}"/>
-    <hyperlink ref="AJ168" r:id="rId16" xr:uid="{E60B9A4B-9B31-40D1-9AD7-7089752E2D2C}"/>
-    <hyperlink ref="AK169" r:id="rId17" xr:uid="{70414161-1662-4518-88C5-B5C611975404}"/>
-    <hyperlink ref="AJ169" r:id="rId18" xr:uid="{88DFB40E-8523-4594-918F-489CF9A4BD50}"/>
-    <hyperlink ref="AL169" r:id="rId19" location="sprg229398" xr:uid="{ACADE52E-07CA-4E41-9DF5-D5BA5975C7AB}"/>
-    <hyperlink ref="AJ170" r:id="rId20" xr:uid="{455BD41A-A2A0-404A-9EB0-82890CFF9839}"/>
-    <hyperlink ref="AJ172" r:id="rId21" location="2-Metadata-update-1" xr:uid="{603BE5D2-639B-41E3-BB09-EC8539E605FB}"/>
-    <hyperlink ref="AJ171" r:id="rId22" location="!tabs-1254736030639" xr:uid="{EE5703CE-F539-4A9F-A731-42AE57EC2313}"/>
-    <hyperlink ref="AI171" r:id="rId23" location="_r=&amp;collection=&amp;country=201&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{A7E232CE-F913-457B-8513-CCCE57CB55BA}"/>
-    <hyperlink ref="AK172" r:id="rId24" xr:uid="{B8FBE934-920C-49E2-92DA-E6FEDA4F595C}"/>
-    <hyperlink ref="AL172" r:id="rId25" location="Kuidas-olla-kindel-et-tegemist-on-statistikaameti-uuringuga-92" xr:uid="{CA7F8719-9551-4F08-9279-44A205DD0254}"/>
-    <hyperlink ref="AJ173" r:id="rId26" xr:uid="{ABB30C57-6C4B-4F67-9AF2-3A77AFDE76F2}"/>
-    <hyperlink ref="AJ174" r:id="rId27" xr:uid="{4698A037-71C9-4156-8076-6E4C1CB98B47}"/>
-    <hyperlink ref="AJ177" r:id="rId28" xr:uid="{BE470730-F027-49A3-92F8-ACC43A3CC2D5}"/>
-    <hyperlink ref="AI179" r:id="rId29" location="_r=&amp;collection=&amp;country=108&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{116D5D4D-41BF-454A-BE56-79FDF145A5DC}"/>
-    <hyperlink ref="AJ179" r:id="rId30" xr:uid="{2D9CFA86-0DB8-4C3A-85BB-B0863CA1A221}"/>
-    <hyperlink ref="AJ180" r:id="rId31" xr:uid="{36E2E48E-EE21-4A4E-B8AD-5EA0A208C8A2}"/>
-    <hyperlink ref="AL180" r:id="rId32" xr:uid="{A4BAC3E4-59C0-4D2E-B20C-1DA705DB55DE}"/>
-    <hyperlink ref="AJ181" r:id="rId33" xr:uid="{E07AFF58-FD64-4499-9976-14A768CF1542}"/>
-    <hyperlink ref="AJ182" r:id="rId34" xr:uid="{46E0BADF-B5E6-4353-BF8F-DAAE781DBB49}"/>
-    <hyperlink ref="AJ184" r:id="rId35" xr:uid="{A4F67C3E-1CEA-44E2-8054-18F11B177783}"/>
-    <hyperlink ref="AK184" r:id="rId36" xr:uid="{88D04B51-A1D6-466B-BB87-BA5198D68139}"/>
-    <hyperlink ref="AJ185" r:id="rId37" location="id=ebb-enquete-beroepsbevolking-2012-2018-0" xr:uid="{C0A7B897-C10F-4E51-992A-1CAE76E144D9}"/>
-    <hyperlink ref="AK185" r:id="rId38" location="/CBS/en/dataset/84166ENG/table?ts=1600877063870" xr:uid="{C433D010-72F3-42E2-8BFA-BAB88CB9F3DD}"/>
-    <hyperlink ref="AJ186" r:id="rId39" xr:uid="{2AC3B5B8-4134-4843-85C5-EF03006AFE0B}"/>
-    <hyperlink ref="AJ187" r:id="rId40" location="gsc.tab=0" xr:uid="{6D9F88B0-960C-4CAF-915B-1CAE580CB114}"/>
-    <hyperlink ref="AI187" r:id="rId41" location="gsc.tab=0" xr:uid="{27C75E78-CBAD-4028-A6BC-E29F54F5452A}"/>
-    <hyperlink ref="AJ188" r:id="rId42" xr:uid="{2EB196D5-6F10-404F-B811-05D7AD4A445E}"/>
-    <hyperlink ref="AJ189" r:id="rId43" xr:uid="{BB8F35DF-F426-4597-9B94-548270094113}"/>
-    <hyperlink ref="AJ190" r:id="rId44" xr:uid="{159E1C12-78A3-45EC-8B48-61053D5F2343}"/>
-    <hyperlink ref="AJ191" r:id="rId45" xr:uid="{ECCD1739-3A3D-410F-A91F-5D0E812D8091}"/>
-    <hyperlink ref="AJ192" r:id="rId46" xr:uid="{ED158EB8-92C9-4C93-B8F2-E3689967E9A7}"/>
-    <hyperlink ref="AJ193" r:id="rId47" xr:uid="{C92CAFD1-1AAF-48A2-97EF-58910B60467E}"/>
-    <hyperlink ref="AJ150" r:id="rId48" xr:uid="{1F9D97E9-D2CC-4D7B-B435-E20B391E7990}"/>
-    <hyperlink ref="AJ175" r:id="rId49" xr:uid="{40B74110-5E36-45EB-9903-3D14F2B0A320}"/>
-    <hyperlink ref="AI162" r:id="rId50" location="_r=&amp;collection=&amp;country=12&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{D7834758-4A75-44E7-84BB-E459592279A0}"/>
-    <hyperlink ref="AK162" r:id="rId51" xr:uid="{11C14D20-36F1-4323-88DC-DC30E1D19381}"/>
-    <hyperlink ref="AJ162" r:id="rId52" xr:uid="{4570E65B-F76A-49E3-A4EC-01EA91D4F1F3}"/>
-    <hyperlink ref="AJ164" r:id="rId53" display="https://www.bahamas.gov.bs/wps/portal/public/key%20statistics/social%20statistics/labour%20force/!ut/p/b1/vZbZrqM4EIaf5TwAHWP2SwiE3QlrAjeIsENIIGwJTz_pVkuj0Uyf3IziurL1lz7X77LlTbg5bcJrPFdFPFa3a3z5OQ_pyBKA5RgcwbOiRAKeJnlGoGxCJunNcXPyA_gQB3URJTvqvFnR-aAabYKqDb0gUXEBpu0HnUhmtDZdM2YivMv1HMXy0U05eG8VTXkoT68LM7JEDn1u-RZisdwDCaP77Ib7Khdku7mFbnonztEtnapbEJ06vicitSOsQUhaSLFg3um1rGWsFjDbNVgzJMiFasAl4anBjl2Vz8s6eYZs54oxumNDvmxJKPFfX68ig1eR4A-DB995AHb47_xvBG88fJMP359B-EtCANnkeZI1ZQrQQPUOBn9gFLgnwW_BdyV-XyR8J8A3wUvA_FHgg427OQEycupnp67NatertZgAR2ZtvraA66iJPORd9mgUEDJs9bW2RyJCzjkALmOr5pgfUt_2BF4cH0qKvQPinwYSnwXKgPw0kP40kPowUAafBsJPA___a6Ftwurc_liS9gf4gVMkRQKaBoDlaAjgxteCJyfe1GUnhbkQxEwyRYN-lVaxYlSr6Tt4c7HuAB38nl2brE2ue2V56OwsbdlG04_eElMTMGXbN3LGFTQXSgUUAj9HW4vOhOJwnTlnsQ9adNqd76_0ISC0FsZ15dyFMe13aZQOAjWWaXbmQJQoZYu17c9nHym3NntjF_sfLW9rJiMDR_RVvMERahgXec3qoD3uSDSOi97iiBaB1p2JpA4Nqfvbri132oH4HZD5MHBPfhr4qwOvQYTOr0-DpNq5FiaJx82B6rSEpFDezrPKS3pvgrJdzxW0ZdTs_XwG6bm-lJ1whCMR4scCw_VtO0Y3sz_QNpMtVXRIhsc4p1WXtSwnUvJ-ts5WWh4HYXdErIxcte_v6wKvzXgK1hNVdhgc54gP1-4eWMUNE7N9SjW5GCkYvK-uOrLD0SFbQ61aOlGmkbSjy27CwpksqlRnl8V1Qr1Tq66kTMu5pVbjhYW9rVSuC55VVuvBZcLyXqUe8cM51VjIlmlk313NqSKkwltZW-rlqE1bc3wqkpEXRj9cuVaIJzjb06ITgGAIVdBN2AHTjzB2VM_L1zuDP91C5P_fQv94U0iWJCGLE4CDDEOx7MavA5oTB7OQVJRr1lgn7JpOcyLEWqxLcmkVHlqw08xce3XqpeF6ZMJLHouFaR8uPSVsz-N8xFYFCv3eypZnt-0aw220fVtbKbS6ztR2SDBRlxbqJZRcItqH22yMHcOYtfACbsnYl_TzFmHSPWP3jeFzjJREGLQ55KMdrWhFRz90H4i36cEK0RIOWRziU7CXzVLxq5N5qkVH7I6yobdYprsWzo98XOT8hUeWX8_jwrELftc2XTvrukHbUo7-HWSM_R3B118_rFt1/dl4/d5/L2dBISEvZ0FBIS9nQSEh/pw/Z7_QB0QSL93A8DE40A64A7B5R3GO1/ren/p=WCM_PI=1/p=urile=wcmQDKpathQDKQCPMOF_ContentQCPinternetQCPDepartmentQCAofQCAStatisticsQCPGovernmentQCPResourcesQCP/p=ns_Z7_QFBB0QFBSL93A8DE40A64A7B5R3GO1_WCM_PreviousPageSize.338701c1-6f1f-41d4-aff2-f0413ea5d543=10/p=ns_Z7_QFBB0QFBSL93A8DE40A64A7B5R3GO1_WCM_Page.338701c1-6f1f-41d4-aff2-f0413ea5d543=1/p=CTX=QCPmof_contentQCPinternetQCPDepartmentQCAofQCAStatisticsQCPGovernmentQCPKeyQCAStatisticsQCPSocialQCAStatisticsQCPLabourQCAForceQCPLabourQCAForce/-/" xr:uid="{44141790-482C-4933-9848-C4050D5F24A7}"/>
-    <hyperlink ref="AI165" r:id="rId54" location="_r=&amp;collection=&amp;country=30&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=&amp;sid=&amp;sk=&amp;sort_by=rank&amp;sort_order=desc&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{D61D0EE8-4F24-4921-AA0B-834CC43778AA}"/>
-    <hyperlink ref="AK165" r:id="rId55" xr:uid="{AC0E4B73-796A-43E9-B287-6D4E5C045CFB}"/>
-    <hyperlink ref="AI166" r:id="rId56" location="_r=&amp;collection=&amp;country=37&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{201896A6-81B1-4D30-AD9F-0193B2864805}"/>
-    <hyperlink ref="AI167" r:id="rId57" location="_r=&amp;collection=&amp;country=208&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{0B68E825-AEA0-4083-8326-F8048D6A54E4}"/>
-    <hyperlink ref="AK170" r:id="rId58" xr:uid="{40B2E3EB-C2D5-4A7C-8474-5803DEE27A17}"/>
-    <hyperlink ref="AI172" r:id="rId59" location="_r=&amp;collection=&amp;country=68,201&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{19ACBC64-03F0-4EA1-9071-344780C8CAE6}"/>
-    <hyperlink ref="AL185" r:id="rId60" xr:uid="{84BC2DA4-CE48-4F5C-92B2-0815014C5DA4}"/>
+    <hyperlink ref="AK149" r:id="rId1" display="https://www.iga.gov.bh/en/category/reports" xr:uid="{13FBE199-AF70-4FE6-B8A7-6B7D021EE558}"/>
+    <hyperlink ref="AK152" r:id="rId2" xr:uid="{B0B6E57C-09A4-4659-82A6-7C5C121A772E}"/>
+    <hyperlink ref="AK153" r:id="rId3" display="http://www.ksh.hu/data_access_safe_centre_access" xr:uid="{FA610065-907B-43A9-BDD4-497A2152D63F}"/>
+    <hyperlink ref="AM163" r:id="rId4" xr:uid="{C0B8B1D7-F697-44E9-950D-0C5A3FBCF76C}"/>
+    <hyperlink ref="AJ178" r:id="rId5" location="_r=&amp;collection=&amp;country=107&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{6C3F1886-6624-4E04-A741-ED3366339968}"/>
+    <hyperlink ref="AK183" r:id="rId6" xr:uid="{5C9BBBFC-7A8C-4EC5-A0CF-C973CFD44550}"/>
+    <hyperlink ref="AL183" r:id="rId7" xr:uid="{B7E3C743-7B39-4D86-9472-8BD2AC324C56}"/>
+    <hyperlink ref="AK157" r:id="rId8" xr:uid="{9094FBC3-21C3-4A32-A7EE-1C38ADE67FA0}"/>
+    <hyperlink ref="AK158" r:id="rId9" location="!/view/en/VBD_SLOVSTAT/pr2018rs/v_pr2018rs_00_00_00_en" xr:uid="{3C3D633D-E51A-48F2-BE9B-B922A980143C}"/>
+    <hyperlink ref="AK159" r:id="rId10" xr:uid="{4806463F-8D0B-4680-AADD-8AA89830D05E}"/>
+    <hyperlink ref="AJ160" r:id="rId11" location="_r=&amp;collection=&amp;country=216&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{4E6F976A-EA20-4694-844D-FA9EEC07C251}"/>
+    <hyperlink ref="AK161" r:id="rId12" xr:uid="{BD4A16C7-AB46-4E49-9D5A-898FCC37723A}"/>
+    <hyperlink ref="AK163" r:id="rId13" xr:uid="{16FD7C52-64A2-41E0-8D08-E0D0F7EF17C9}"/>
+    <hyperlink ref="AL163" r:id="rId14" location="figures" xr:uid="{832B8C73-1423-4F9E-955F-82089634F0C4}"/>
+    <hyperlink ref="AK166" r:id="rId15" xr:uid="{FA867C7F-7376-4FF1-B16C-3853F9D287BD}"/>
+    <hyperlink ref="AK168" r:id="rId16" xr:uid="{E60B9A4B-9B31-40D1-9AD7-7089752E2D2C}"/>
+    <hyperlink ref="AL169" r:id="rId17" xr:uid="{70414161-1662-4518-88C5-B5C611975404}"/>
+    <hyperlink ref="AK169" r:id="rId18" xr:uid="{88DFB40E-8523-4594-918F-489CF9A4BD50}"/>
+    <hyperlink ref="AM169" r:id="rId19" location="sprg229398" xr:uid="{ACADE52E-07CA-4E41-9DF5-D5BA5975C7AB}"/>
+    <hyperlink ref="AK170" r:id="rId20" xr:uid="{455BD41A-A2A0-404A-9EB0-82890CFF9839}"/>
+    <hyperlink ref="AK172" r:id="rId21" location="2-Metadata-update-1" xr:uid="{603BE5D2-639B-41E3-BB09-EC8539E605FB}"/>
+    <hyperlink ref="AK171" r:id="rId22" location="!tabs-1254736030639" xr:uid="{EE5703CE-F539-4A9F-A731-42AE57EC2313}"/>
+    <hyperlink ref="AJ171" r:id="rId23" location="_r=&amp;collection=&amp;country=201&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{A7E232CE-F913-457B-8513-CCCE57CB55BA}"/>
+    <hyperlink ref="AL172" r:id="rId24" xr:uid="{B8FBE934-920C-49E2-92DA-E6FEDA4F595C}"/>
+    <hyperlink ref="AM172" r:id="rId25" location="Kuidas-olla-kindel-et-tegemist-on-statistikaameti-uuringuga-92" xr:uid="{CA7F8719-9551-4F08-9279-44A205DD0254}"/>
+    <hyperlink ref="AK173" r:id="rId26" xr:uid="{ABB30C57-6C4B-4F67-9AF2-3A77AFDE76F2}"/>
+    <hyperlink ref="AK174" r:id="rId27" xr:uid="{4698A037-71C9-4156-8076-6E4C1CB98B47}"/>
+    <hyperlink ref="AK177" r:id="rId28" xr:uid="{BE470730-F027-49A3-92F8-ACC43A3CC2D5}"/>
+    <hyperlink ref="AJ179" r:id="rId29" location="_r=&amp;collection=&amp;country=108&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{116D5D4D-41BF-454A-BE56-79FDF145A5DC}"/>
+    <hyperlink ref="AK179" r:id="rId30" xr:uid="{2D9CFA86-0DB8-4C3A-85BB-B0863CA1A221}"/>
+    <hyperlink ref="AK180" r:id="rId31" xr:uid="{36E2E48E-EE21-4A4E-B8AD-5EA0A208C8A2}"/>
+    <hyperlink ref="AM180" r:id="rId32" xr:uid="{A4BAC3E4-59C0-4D2E-B20C-1DA705DB55DE}"/>
+    <hyperlink ref="AK181" r:id="rId33" xr:uid="{E07AFF58-FD64-4499-9976-14A768CF1542}"/>
+    <hyperlink ref="AK182" r:id="rId34" xr:uid="{46E0BADF-B5E6-4353-BF8F-DAAE781DBB49}"/>
+    <hyperlink ref="AK184" r:id="rId35" xr:uid="{A4F67C3E-1CEA-44E2-8054-18F11B177783}"/>
+    <hyperlink ref="AL184" r:id="rId36" xr:uid="{88D04B51-A1D6-466B-BB87-BA5198D68139}"/>
+    <hyperlink ref="AK185" r:id="rId37" location="id=ebb-enquete-beroepsbevolking-2012-2018-0" xr:uid="{C0A7B897-C10F-4E51-992A-1CAE76E144D9}"/>
+    <hyperlink ref="AL185" r:id="rId38" location="/CBS/en/dataset/84166ENG/table?ts=1600877063870" xr:uid="{C433D010-72F3-42E2-8BFA-BAB88CB9F3DD}"/>
+    <hyperlink ref="AK186" r:id="rId39" xr:uid="{2AC3B5B8-4134-4843-85C5-EF03006AFE0B}"/>
+    <hyperlink ref="AK187" r:id="rId40" location="gsc.tab=0" xr:uid="{6D9F88B0-960C-4CAF-915B-1CAE580CB114}"/>
+    <hyperlink ref="AJ187" r:id="rId41" location="gsc.tab=0" xr:uid="{27C75E78-CBAD-4028-A6BC-E29F54F5452A}"/>
+    <hyperlink ref="AK188" r:id="rId42" xr:uid="{2EB196D5-6F10-404F-B811-05D7AD4A445E}"/>
+    <hyperlink ref="AK189" r:id="rId43" xr:uid="{BB8F35DF-F426-4597-9B94-548270094113}"/>
+    <hyperlink ref="AK190" r:id="rId44" xr:uid="{159E1C12-78A3-45EC-8B48-61053D5F2343}"/>
+    <hyperlink ref="AK191" r:id="rId45" xr:uid="{ECCD1739-3A3D-410F-A91F-5D0E812D8091}"/>
+    <hyperlink ref="AK192" r:id="rId46" xr:uid="{ED158EB8-92C9-4C93-B8F2-E3689967E9A7}"/>
+    <hyperlink ref="AK193" r:id="rId47" xr:uid="{C92CAFD1-1AAF-48A2-97EF-58910B60467E}"/>
+    <hyperlink ref="AK150" r:id="rId48" xr:uid="{1F9D97E9-D2CC-4D7B-B435-E20B391E7990}"/>
+    <hyperlink ref="AK175" r:id="rId49" xr:uid="{40B74110-5E36-45EB-9903-3D14F2B0A320}"/>
+    <hyperlink ref="AJ162" r:id="rId50" location="_r=&amp;collection=&amp;country=12&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{D7834758-4A75-44E7-84BB-E459592279A0}"/>
+    <hyperlink ref="AL162" r:id="rId51" xr:uid="{11C14D20-36F1-4323-88DC-DC30E1D19381}"/>
+    <hyperlink ref="AK162" r:id="rId52" xr:uid="{4570E65B-F76A-49E3-A4EC-01EA91D4F1F3}"/>
+    <hyperlink ref="AK164" r:id="rId53" display="https://www.bahamas.gov.bs/wps/portal/public/key%20statistics/social%20statistics/labour%20force/!ut/p/b1/vZbZrqM4EIaf5TwAHWP2SwiE3QlrAjeIsENIIGwJTz_pVkuj0Uyf3IziurL1lz7X77LlTbg5bcJrPFdFPFa3a3z5OQ_pyBKA5RgcwbOiRAKeJnlGoGxCJunNcXPyA_gQB3URJTvqvFnR-aAabYKqDb0gUXEBpu0HnUhmtDZdM2YivMv1HMXy0U05eG8VTXkoT68LM7JEDn1u-RZisdwDCaP77Ib7Khdku7mFbnonztEtnapbEJ06vicitSOsQUhaSLFg3um1rGWsFjDbNVgzJMiFasAl4anBjl2Vz8s6eYZs54oxumNDvmxJKPFfX68ig1eR4A-DB995AHb47_xvBG88fJMP359B-EtCANnkeZI1ZQrQQPUOBn9gFLgnwW_BdyV-XyR8J8A3wUvA_FHgg427OQEycupnp67NatertZgAR2ZtvraA66iJPORd9mgUEDJs9bW2RyJCzjkALmOr5pgfUt_2BF4cH0qKvQPinwYSnwXKgPw0kP40kPowUAafBsJPA___a6Ftwurc_liS9gf4gVMkRQKaBoDlaAjgxteCJyfe1GUnhbkQxEwyRYN-lVaxYlSr6Tt4c7HuAB38nl2brE2ue2V56OwsbdlG04_eElMTMGXbN3LGFTQXSgUUAj9HW4vOhOJwnTlnsQ9adNqd76_0ISC0FsZ15dyFMe13aZQOAjWWaXbmQJQoZYu17c9nHym3NntjF_sfLW9rJiMDR_RVvMERahgXec3qoD3uSDSOi97iiBaB1p2JpA4Nqfvbri132oH4HZD5MHBPfhr4qwOvQYTOr0-DpNq5FiaJx82B6rSEpFDezrPKS3pvgrJdzxW0ZdTs_XwG6bm-lJ1whCMR4scCw_VtO0Y3sz_QNpMtVXRIhsc4p1WXtSwnUvJ-ts5WWh4HYXdErIxcte_v6wKvzXgK1hNVdhgc54gP1-4eWMUNE7N9SjW5GCkYvK-uOrLD0SFbQ61aOlGmkbSjy27CwpksqlRnl8V1Qr1Tq66kTMu5pVbjhYW9rVSuC55VVuvBZcLyXqUe8cM51VjIlmlk313NqSKkwltZW-rlqE1bc3wqkpEXRj9cuVaIJzjb06ITgGAIVdBN2AHTjzB2VM_L1zuDP91C5P_fQv94U0iWJCGLE4CDDEOx7MavA5oTB7OQVJRr1lgn7JpOcyLEWqxLcmkVHlqw08xce3XqpeF6ZMJLHouFaR8uPSVsz-N8xFYFCv3eypZnt-0aw220fVtbKbS6ztR2SDBRlxbqJZRcItqH22yMHcOYtfACbsnYl_TzFmHSPWP3jeFzjJREGLQ55KMdrWhFRz90H4i36cEK0RIOWRziU7CXzVLxq5N5qkVH7I6yobdYprsWzo98XOT8hUeWX8_jwrELftc2XTvrukHbUo7-HWSM_R3B118_rFt1/dl4/d5/L2dBISEvZ0FBIS9nQSEh/pw/Z7_QB0QSL93A8DE40A64A7B5R3GO1/ren/p=WCM_PI=1/p=urile=wcmQDKpathQDKQCPMOF_ContentQCPinternetQCPDepartmentQCAofQCAStatisticsQCPGovernmentQCPResourcesQCP/p=ns_Z7_QFBB0QFBSL93A8DE40A64A7B5R3GO1_WCM_PreviousPageSize.338701c1-6f1f-41d4-aff2-f0413ea5d543=10/p=ns_Z7_QFBB0QFBSL93A8DE40A64A7B5R3GO1_WCM_Page.338701c1-6f1f-41d4-aff2-f0413ea5d543=1/p=CTX=QCPmof_contentQCPinternetQCPDepartmentQCAofQCAStatisticsQCPGovernmentQCPKeyQCAStatisticsQCPSocialQCAStatisticsQCPLabourQCAForceQCPLabourQCAForce/-/" xr:uid="{44141790-482C-4933-9848-C4050D5F24A7}"/>
+    <hyperlink ref="AJ165" r:id="rId54" location="_r=&amp;collection=&amp;country=30&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=&amp;sid=&amp;sk=&amp;sort_by=rank&amp;sort_order=desc&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{D61D0EE8-4F24-4921-AA0B-834CC43778AA}"/>
+    <hyperlink ref="AL165" r:id="rId55" xr:uid="{AC0E4B73-796A-43E9-B287-6D4E5C045CFB}"/>
+    <hyperlink ref="AJ166" r:id="rId56" location="_r=&amp;collection=&amp;country=37&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{201896A6-81B1-4D30-AD9F-0193B2864805}"/>
+    <hyperlink ref="AJ167" r:id="rId57" location="_r=&amp;collection=&amp;country=208&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{0B68E825-AEA0-4083-8326-F8048D6A54E4}"/>
+    <hyperlink ref="AL170" r:id="rId58" xr:uid="{40B2E3EB-C2D5-4A7C-8474-5803DEE27A17}"/>
+    <hyperlink ref="AJ172" r:id="rId59" location="_r=&amp;collection=&amp;country=68,201&amp;dtype=&amp;from=1975&amp;page=1&amp;ps=100&amp;sid=&amp;sk=&amp;sort_by=nation&amp;sort_order=&amp;to=2019&amp;topic=&amp;view=s&amp;vk=" xr:uid="{19ACBC64-03F0-4EA1-9071-344780C8CAE6}"/>
+    <hyperlink ref="AM185" r:id="rId60" xr:uid="{84BC2DA4-CE48-4F5C-92B2-0815014C5DA4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId61"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId62"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3e02667f-0271-471b-bd6e-11a2e16def1d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b19ad29f-88fa-4d62-ac16-34b992563bf9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ADB9CD767C4FF34281D6635032C5B89D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3b7ad1acb7d07f4c67b79ea712f2c443">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b19ad29f-88fa-4d62-ac16-34b992563bf9" xmlns:ns3="e781ea9d-1795-4792-8d8d-c86ae526af93" xmlns:ns4="3e02667f-0271-471b-bd6e-11a2e16def1d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e0bd56705adf4bb69ae57d53dbdc9cd2" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
@@ -41496,14 +41741,68 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3e02667f-0271-471b-bd6e-11a2e16def1d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b19ad29f-88fa-4d62-ac16-34b992563bf9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8001F0D6-2591-4A68-815D-C98503A36C32}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6BFF356-860D-46A7-9D5F-7C3887335AD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
+    <ds:schemaRef ds:uri="e781ea9d-1795-4792-8d8d-c86ae526af93"/>
+    <ds:schemaRef ds:uri="3e02667f-0271-471b-bd6e-11a2e16def1d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACEEE91F-8CDF-4F2C-85D3-58EC881B6941}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACEEE91F-8CDF-4F2C-85D3-58EC881B6941}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3e02667f-0271-471b-bd6e-11a2e16def1d"/>
+    <ds:schemaRef ds:uri="e781ea9d-1795-4792-8d8d-c86ae526af93"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6BFF356-860D-46A7-9D5F-7C3887335AD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8001F0D6-2591-4A68-815D-C98503A36C32}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>